--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\5_MB MMA\09_Information\10_FTQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB48A97B-972B-445A-87C5-02BE51DEDE70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D44759-09D7-4A13-BF59-33E41A7C989E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$90</definedName>
     <definedName name="DATA_01">[1]Data_Lineal!$H$4:$Y$30</definedName>
     <definedName name="DB_01">#REF!</definedName>
     <definedName name="DB_CAP01">'[2]CAPACIDAD (1)'!$X$9:$AM$29</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="81">
   <si>
     <t>*</t>
   </si>
@@ -162,9 +162,6 @@
     <t>Falla de inspección visual en curvas sin NG Op.100</t>
   </si>
   <si>
-    <t>Falla por falta de caída de SAS por gravedad sin NG Op.200</t>
-  </si>
-  <si>
     <t>Dispensado de Grasa No Uniforme en Engrane sin NG Op.200</t>
   </si>
   <si>
@@ -181,9 +178,6 @@
   </si>
   <si>
     <t>Falla de Etiqueta por Guarda sin NG Op.300</t>
-  </si>
-  <si>
-    <t>Falla de inspección visual  Op.600</t>
   </si>
   <si>
     <t>Inspección visual  no detecta PCB sin conector Op.600</t>
@@ -238,6 +232,81 @@
   </si>
   <si>
     <t>Falla 3121.022 Op.EOL</t>
+  </si>
+  <si>
+    <t>Calibrador</t>
+  </si>
+  <si>
+    <t>Mal ensamble por falla en detección de Elemento de compensación Op.400</t>
+  </si>
+  <si>
+    <t>Atorramiento de pieza en Nido Op.600</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual en puntos de grasa Op.600</t>
+  </si>
+  <si>
+    <t>Pruebas de Ruido</t>
+  </si>
+  <si>
+    <t>Calibrador de iluminación</t>
+  </si>
+  <si>
+    <t>Falla por mal ensamble de SAS por gravedad sin NG Op.200</t>
+  </si>
+  <si>
+    <t>Se interrumpen cortinas de emergencia, detiene proceso Op.300</t>
+  </si>
+  <si>
+    <t>Banda transportadora no detecta piezas, se caen Op.600</t>
+  </si>
+  <si>
+    <t>Mal enclipsado de Spiral Op.700</t>
+  </si>
+  <si>
+    <t>Se interrumpen cortinas de emergencia, detiene proceso Op.800</t>
+  </si>
+  <si>
+    <t>Calibrador de Palancas</t>
+  </si>
+  <si>
+    <t>Falla por limites en Palancas Op.Calibrador de Palancas</t>
+  </si>
+  <si>
+    <t>Falla de sensor, no detecta pieza Op.Pruebas de Ruido</t>
+  </si>
+  <si>
+    <t>07/09/2026</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>12289507</t>
+  </si>
+  <si>
+    <t>Falla en proceso, no regresa Palanca a posición Op.Pruebas de Ruido</t>
+  </si>
+  <si>
+    <t>No inicia secuencia Op.Pruebas de Ruido</t>
+  </si>
+  <si>
+    <t>Calibrador de Iluminación</t>
+  </si>
+  <si>
+    <t>No inicia secuencia Op.Calibrador de Iluminación</t>
+  </si>
+  <si>
+    <t>Calibrador SAS1</t>
+  </si>
+  <si>
+    <t>Calibrador SAS2</t>
+  </si>
+  <si>
+    <t>Falla 9220.120 Op.Calibrador SAS1</t>
+  </si>
+  <si>
+    <t>Falla 4000.130 Op.Calibrador SAS2</t>
   </si>
 </sst>
 </file>
@@ -319,7 +388,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -356,6 +425,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -24342,7 +24414,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K66" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K90" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CDAA4D20-2955-41E2-BD7E-9330E166FFF4}" name="Fecha" dataDxfId="18"/>
     <tableColumn id="9" xr3:uid="{F70BB124-92DE-4024-874C-EE3BA966CDE6}" name="Semana" dataDxfId="17">
@@ -24368,15 +24440,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S66" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S84" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="Fecha" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="Semana" dataDxfId="5">
-      <calculatedColumnFormula>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="07/09/2026" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="37" dataDxfId="5">
+      <calculatedColumnFormula>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2BBDA3EE-1089-4999-82D7-821DAA1CF033}" name="Línea" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{A327B0AF-C947-4083-8F0A-4A5908FD3558}" name="Maquina" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{58C9F38E-D89E-450A-9CAA-EFCECBECC74C}" name="Version" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{2BBDA3EE-1089-4999-82D7-821DAA1CF033}" name="SCCM MMA" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{A327B0AF-C947-4083-8F0A-4A5908FD3558}" name="Pruebas de Ruido" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{58C9F38E-D89E-450A-9CAA-EFCECBECC74C}" name="12289507" dataDxfId="2"/>
     <tableColumn id="5" xr3:uid="{5C95C72F-200A-46B3-A6FC-20E7D88A7BCD}" name="Defecto" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{33109690-8A43-4F38-8F52-FD73CBA9F32F}" name="Cantidad" dataDxfId="0"/>
   </tableColumns>
@@ -24648,13 +24720,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A1B645-8848-474A-88BA-FA9209B01B4F}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V828"/>
+  <dimension ref="A1:V824"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
     <col min="2" max="2" width="13.21875" style="1" customWidth="1"/>
     <col min="3" max="4" width="11.5546875" style="1"/>
-    <col min="5" max="5" width="14.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.21875" style="1" customWidth="1"/>
     <col min="6" max="7" width="11.5546875" style="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="1" hidden="1" customWidth="1"/>
@@ -24664,9 +24736,9 @@
     <col min="13" max="13" width="13.88671875" style="1" customWidth="1"/>
     <col min="14" max="14" width="10.5546875" style="1" customWidth="1"/>
     <col min="15" max="15" width="12.44140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23" style="1" customWidth="1"/>
     <col min="17" max="17" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="70.21875" style="1" customWidth="1"/>
     <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -24751,20 +24823,20 @@
       <c r="K4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>6</v>
+      <c r="M4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>3</v>
+        <v>60</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>72</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>2</v>
@@ -24812,7 +24884,7 @@
         <v>46224</v>
       </c>
       <c r="N5" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>30</v>
       </c>
       <c r="O5" s="1" t="s">
@@ -24870,7 +24942,7 @@
         <v>46226</v>
       </c>
       <c r="N6" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>30</v>
       </c>
       <c r="O6" s="1" t="s">
@@ -24928,7 +25000,7 @@
         <v>46226</v>
       </c>
       <c r="N7" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>30</v>
       </c>
       <c r="O7" s="1" t="s">
@@ -24986,7 +25058,7 @@
         <v>46226</v>
       </c>
       <c r="N8" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>30</v>
       </c>
       <c r="O8" s="1" t="s">
@@ -25044,7 +25116,7 @@
         <v>46226</v>
       </c>
       <c r="N9" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>30</v>
       </c>
       <c r="O9" s="1" t="s">
@@ -25102,7 +25174,7 @@
         <v>46226</v>
       </c>
       <c r="N10" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>30</v>
       </c>
       <c r="O10" s="1" t="s">
@@ -25160,7 +25232,7 @@
         <v>46226</v>
       </c>
       <c r="N11" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>30</v>
       </c>
       <c r="O11" s="1" t="s">
@@ -25218,7 +25290,7 @@
         <v>46226</v>
       </c>
       <c r="N12" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>30</v>
       </c>
       <c r="O12" s="1" t="s">
@@ -25276,7 +25348,7 @@
         <v>46226</v>
       </c>
       <c r="N13" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>30</v>
       </c>
       <c r="O13" s="1" t="s">
@@ -25334,7 +25406,7 @@
         <v>46226</v>
       </c>
       <c r="N14" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>30</v>
       </c>
       <c r="O14" s="1" t="s">
@@ -25392,7 +25464,7 @@
         <v>46226</v>
       </c>
       <c r="N15" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>30</v>
       </c>
       <c r="O15" s="1" t="s">
@@ -25450,7 +25522,7 @@
         <v>46226</v>
       </c>
       <c r="N16" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>30</v>
       </c>
       <c r="O16" s="1" t="s">
@@ -25508,7 +25580,7 @@
         <v>46226</v>
       </c>
       <c r="N17" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>30</v>
       </c>
       <c r="O17" s="1" t="s">
@@ -25566,7 +25638,7 @@
         <v>46226</v>
       </c>
       <c r="N18" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>30</v>
       </c>
       <c r="O18" s="1" t="s">
@@ -25624,7 +25696,7 @@
         <v>46230</v>
       </c>
       <c r="N19" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O19" s="1" t="s">
@@ -25682,7 +25754,7 @@
         <v>46230</v>
       </c>
       <c r="N20" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O20" s="1" t="s">
@@ -25695,7 +25767,7 @@
         <v>12289497</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="S20" s="1">
         <v>6</v>
@@ -25740,7 +25812,7 @@
         <v>46230</v>
       </c>
       <c r="N21" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O21" s="1" t="s">
@@ -25753,7 +25825,7 @@
         <v>12289497</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="S21" s="1">
         <v>12</v>
@@ -25798,7 +25870,7 @@
         <v>46231</v>
       </c>
       <c r="N22" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O22" s="1" t="s">
@@ -25856,7 +25928,7 @@
         <v>46231</v>
       </c>
       <c r="N23" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O23" s="1" t="s">
@@ -25869,7 +25941,7 @@
         <v>12289497</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S23" s="1">
         <v>9</v>
@@ -25914,7 +25986,7 @@
         <v>46231</v>
       </c>
       <c r="N24" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O24" s="1" t="s">
@@ -25927,7 +25999,7 @@
         <v>12289497</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S24" s="1">
         <v>6</v>
@@ -25972,7 +26044,7 @@
         <v>46231</v>
       </c>
       <c r="N25" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O25" s="1" t="s">
@@ -25985,7 +26057,7 @@
         <v>12289497</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S25" s="1">
         <v>45</v>
@@ -26030,7 +26102,7 @@
         <v>46231</v>
       </c>
       <c r="N26" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O26" s="1" t="s">
@@ -26043,7 +26115,7 @@
         <v>12289497</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S26" s="1">
         <v>3</v>
@@ -26088,7 +26160,7 @@
         <v>46234</v>
       </c>
       <c r="N27" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O27" s="1" t="s">
@@ -26146,7 +26218,7 @@
         <v>46234</v>
       </c>
       <c r="N28" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O28" s="1" t="s">
@@ -26159,7 +26231,7 @@
         <v>12289475</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S28" s="1">
         <v>5</v>
@@ -26204,7 +26276,7 @@
         <v>46234</v>
       </c>
       <c r="N29" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O29" s="1" t="s">
@@ -26217,7 +26289,7 @@
         <v>12289475</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S29" s="1">
         <v>3</v>
@@ -26262,7 +26334,7 @@
         <v>46234</v>
       </c>
       <c r="N30" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O30" s="1" t="s">
@@ -26275,7 +26347,7 @@
         <v>12289475</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S30" s="1">
         <v>22</v>
@@ -26320,7 +26392,7 @@
         <v>46234</v>
       </c>
       <c r="N31" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O31" s="1" t="s">
@@ -26333,7 +26405,7 @@
         <v>12289475</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="S31" s="1">
         <v>3</v>
@@ -26378,7 +26450,7 @@
         <v>46234</v>
       </c>
       <c r="N32" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O32" s="1" t="s">
@@ -26391,7 +26463,7 @@
         <v>12289475</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="S32" s="1">
         <v>2</v>
@@ -26436,7 +26508,7 @@
         <v>46234</v>
       </c>
       <c r="N33" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O33" s="1" t="s">
@@ -26449,7 +26521,7 @@
         <v>12289475</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="S33" s="1">
         <v>2</v>
@@ -26494,7 +26566,7 @@
         <v>46234</v>
       </c>
       <c r="N34" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O34" s="1" t="s">
@@ -26507,7 +26579,7 @@
         <v>12289475</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="S34" s="1">
         <v>2</v>
@@ -26552,7 +26624,7 @@
         <v>46238</v>
       </c>
       <c r="N35" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O35" s="1" t="s">
@@ -26565,7 +26637,7 @@
         <v>12289497</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="S35" s="1">
         <v>6</v>
@@ -26610,7 +26682,7 @@
         <v>46238</v>
       </c>
       <c r="N36" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O36" s="1" t="s">
@@ -26623,7 +26695,7 @@
         <v>12289497</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="S36" s="1">
         <v>3</v>
@@ -26668,7 +26740,7 @@
         <v>46238</v>
       </c>
       <c r="N37" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O37" s="1" t="s">
@@ -26726,7 +26798,7 @@
         <v>46238</v>
       </c>
       <c r="N38" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O38" s="1" t="s">
@@ -26739,7 +26811,7 @@
         <v>12289497</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S38" s="1">
         <v>5</v>
@@ -26784,7 +26856,7 @@
         <v>46238</v>
       </c>
       <c r="N39" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O39" s="1" t="s">
@@ -26842,7 +26914,7 @@
         <v>46238</v>
       </c>
       <c r="N40" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O40" s="1" t="s">
@@ -26855,7 +26927,7 @@
         <v>12289497</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S40" s="1">
         <v>15</v>
@@ -26900,7 +26972,7 @@
         <v>46238</v>
       </c>
       <c r="N41" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O41" s="1" t="s">
@@ -26913,7 +26985,7 @@
         <v>12289497</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S41" s="1">
         <v>5</v>
@@ -26958,7 +27030,7 @@
         <v>46232</v>
       </c>
       <c r="N42" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O42" s="1" t="s">
@@ -26971,7 +27043,7 @@
         <v>10532587</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="S42" s="1">
         <v>13</v>
@@ -27016,7 +27088,7 @@
         <v>46232</v>
       </c>
       <c r="N43" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O43" s="1" t="s">
@@ -27029,7 +27101,7 @@
         <v>10532587</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S43" s="1">
         <v>18</v>
@@ -27074,7 +27146,7 @@
         <v>46232</v>
       </c>
       <c r="N44" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O44" s="1" t="s">
@@ -27132,7 +27204,7 @@
         <v>46232</v>
       </c>
       <c r="N45" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O45" s="1" t="s">
@@ -27145,7 +27217,7 @@
         <v>10532587</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S45" s="1">
         <v>15</v>
@@ -27190,7 +27262,7 @@
         <v>46232</v>
       </c>
       <c r="N46" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O46" s="1" t="s">
@@ -27203,7 +27275,7 @@
         <v>10532587</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S46" s="1">
         <v>1</v>
@@ -27248,7 +27320,7 @@
         <v>46232</v>
       </c>
       <c r="N47" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O47" s="1" t="s">
@@ -27261,7 +27333,7 @@
         <v>10532587</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S47" s="1">
         <v>6</v>
@@ -27306,7 +27378,7 @@
         <v>46232</v>
       </c>
       <c r="N48" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O48" s="1" t="s">
@@ -27319,7 +27391,7 @@
         <v>10532587</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="S48" s="1">
         <v>27</v>
@@ -27364,7 +27436,7 @@
         <v>46232</v>
       </c>
       <c r="N49" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O49" s="1" t="s">
@@ -27422,7 +27494,7 @@
         <v>46232</v>
       </c>
       <c r="N50" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O50" s="1" t="s">
@@ -27435,7 +27507,7 @@
         <v>10532587</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S50" s="1">
         <v>2</v>
@@ -27480,7 +27552,7 @@
         <v>46232</v>
       </c>
       <c r="N51" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>31</v>
       </c>
       <c r="O51" s="1" t="s">
@@ -27538,7 +27610,7 @@
         <v>46239</v>
       </c>
       <c r="N52" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O52" s="1" t="s">
@@ -27551,7 +27623,7 @@
         <v>10532587</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="S52" s="1">
         <v>9</v>
@@ -27596,7 +27668,7 @@
         <v>46239</v>
       </c>
       <c r="N53" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O53" s="1" t="s">
@@ -27609,7 +27681,7 @@
         <v>10532587</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S53" s="1">
         <v>5</v>
@@ -27654,7 +27726,7 @@
         <v>46239</v>
       </c>
       <c r="N54" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O54" s="1" t="s">
@@ -27667,7 +27739,7 @@
         <v>10532587</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S54" s="1">
         <v>18</v>
@@ -27712,7 +27784,7 @@
         <v>46237</v>
       </c>
       <c r="N55" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O55" s="1" t="s">
@@ -27725,7 +27797,7 @@
         <v>10532587</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S55" s="1">
         <v>6</v>
@@ -27770,7 +27842,7 @@
         <v>46239</v>
       </c>
       <c r="N56" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O56" s="1" t="s">
@@ -27828,7 +27900,7 @@
         <v>46239</v>
       </c>
       <c r="N57" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O57" s="1" t="s">
@@ -27841,7 +27913,7 @@
         <v>10532587</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S57" s="1">
         <v>2</v>
@@ -27886,7 +27958,7 @@
         <v>46237</v>
       </c>
       <c r="N58" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O58" s="1" t="s">
@@ -27944,7 +28016,7 @@
         <v>46237</v>
       </c>
       <c r="N59" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O59" s="1" t="s">
@@ -27957,7 +28029,7 @@
         <v>10532587</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="S59" s="1">
         <v>10</v>
@@ -28002,7 +28074,7 @@
         <v>46237</v>
       </c>
       <c r="N60" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O60" s="1" t="s">
@@ -28015,7 +28087,7 @@
         <v>10532587</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S60" s="1">
         <v>2</v>
@@ -28060,7 +28132,7 @@
         <v>46237</v>
       </c>
       <c r="N61" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O61" s="1" t="s">
@@ -28073,7 +28145,7 @@
         <v>10532587</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S61" s="1">
         <v>2</v>
@@ -28118,7 +28190,7 @@
         <v>46237</v>
       </c>
       <c r="N62" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O62" s="1" t="s">
@@ -28131,7 +28203,7 @@
         <v>10532587</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S62" s="1">
         <v>1</v>
@@ -28176,7 +28248,7 @@
         <v>46237</v>
       </c>
       <c r="N63" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O63" s="1" t="s">
@@ -28189,7 +28261,7 @@
         <v>10532587</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="S63" s="1">
         <v>1</v>
@@ -28234,7 +28306,7 @@
         <v>46239</v>
       </c>
       <c r="N64" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O64" s="1" t="s">
@@ -28292,7 +28364,7 @@
         <v>46239</v>
       </c>
       <c r="N65" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O65" s="1" t="s">
@@ -28350,7 +28422,7 @@
         <v>46239</v>
       </c>
       <c r="N66" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>32</v>
       </c>
       <c r="O66" s="1" t="s">
@@ -28363,220 +28435,1314 @@
         <v>10532587</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="S66" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B67" s="4"/>
-      <c r="F67" s="9"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="11"/>
-      <c r="M67" s="4"/>
-      <c r="Q67" s="9"/>
+      <c r="B67" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C67" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" s="1">
+        <v>100</v>
+      </c>
+      <c r="F67" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G67" s="1">
+        <v>15</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="13">
+        <f t="shared" ref="J67:J75" si="9">ABS(G$3-I67)</f>
+        <v>1</v>
+      </c>
+      <c r="K67" s="11">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M67" s="4">
+        <v>46269</v>
+      </c>
+      <c r="N67" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>36</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P67" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S67" s="1">
+        <v>6</v>
+      </c>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B68" s="4"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="5"/>
-      <c r="M68" s="4"/>
-      <c r="Q68" s="9"/>
+      <c r="B68" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C68" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" s="1">
+        <v>200</v>
+      </c>
+      <c r="F68" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G68" s="1">
+        <v>15</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+      <c r="I68" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J68" s="13">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="K68" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M68" s="4">
+        <v>46269</v>
+      </c>
+      <c r="N68" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>36</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P68" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q68" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S68" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B69" s="4"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="5"/>
-      <c r="M69" s="4"/>
-      <c r="Q69" s="9"/>
+      <c r="B69" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C69" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E69" s="1">
+        <v>300</v>
+      </c>
+      <c r="F69" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G69" s="1">
+        <v>15</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+      <c r="I69" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J69" s="13">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="K69" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M69" s="4">
+        <v>46269</v>
+      </c>
+      <c r="N69" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>36</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P69" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q69" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R69" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="S69" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B70" s="4"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="5"/>
-      <c r="M70" s="4"/>
+      <c r="B70" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C70" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E70" s="1">
+        <v>400</v>
+      </c>
+      <c r="F70" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G70" s="1">
+        <v>15</v>
+      </c>
+      <c r="H70" s="1">
+        <v>6</v>
+      </c>
+      <c r="I70" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.4</v>
+      </c>
+      <c r="J70" s="13">
+        <f t="shared" si="9"/>
+        <v>0.6</v>
+      </c>
+      <c r="K70" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.6</v>
+      </c>
+      <c r="M70" s="4">
+        <v>46269</v>
+      </c>
+      <c r="N70" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>36</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P70" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q70" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="S70" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B71" s="4"/>
-      <c r="I71" s="3"/>
-      <c r="J71" s="1"/>
-      <c r="K71" s="5"/>
-      <c r="M71" s="4"/>
+      <c r="B71" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C71" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" s="1">
+        <v>500</v>
+      </c>
+      <c r="F71" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G71" s="1">
+        <v>15</v>
+      </c>
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+      <c r="I71" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J71" s="13">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="K71" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M71" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N71" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P71" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q71" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R71" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="S71" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B72" s="4"/>
-      <c r="I72" s="3"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="5"/>
-      <c r="M72" s="4"/>
+      <c r="B72" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C72" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E72" s="1">
+        <v>600</v>
+      </c>
+      <c r="F72" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G72" s="1">
+        <v>15</v>
+      </c>
+      <c r="H72" s="1">
+        <v>6</v>
+      </c>
+      <c r="I72" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.4</v>
+      </c>
+      <c r="J72" s="13">
+        <f t="shared" si="9"/>
+        <v>0.6</v>
+      </c>
+      <c r="K72" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.6</v>
+      </c>
+      <c r="M72" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N72" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P72" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q72" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R72" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S72" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B73" s="4"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="5"/>
-      <c r="M73" s="4"/>
+      <c r="B73" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C73" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E73" s="1">
+        <v>700</v>
+      </c>
+      <c r="F73" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G73" s="1">
+        <v>15</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+      <c r="I73" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J73" s="13">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="K73" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M73" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N73" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P73" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q73" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R73" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S73" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B74" s="4"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="5"/>
-      <c r="M74" s="4"/>
+      <c r="B74" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C74" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E74" s="1">
+        <v>800</v>
+      </c>
+      <c r="F74" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G74" s="1">
+        <v>15</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+      <c r="I74" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J74" s="13">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="K74" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M74" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N74" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P74" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q74" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R74" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="S74" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B75" s="4"/>
-      <c r="I75" s="3"/>
-      <c r="J75" s="1"/>
-      <c r="K75" s="5"/>
-      <c r="M75" s="4"/>
+      <c r="B75" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C75" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F75" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G75" s="1">
+        <v>15</v>
+      </c>
+      <c r="H75" s="1">
+        <v>0</v>
+      </c>
+      <c r="I75" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J75" s="13">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="K75" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M75" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N75" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P75" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q75" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R75" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S75" s="1">
+        <v>50</v>
+      </c>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B76" s="4"/>
-      <c r="I76" s="3"/>
-      <c r="J76" s="1"/>
-      <c r="K76" s="5"/>
-      <c r="M76" s="4"/>
+      <c r="B76" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C76" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F76" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G76" s="1">
+        <v>14</v>
+      </c>
+      <c r="H76" s="1">
+        <v>9</v>
+      </c>
+      <c r="I76" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="J76" s="13">
+        <f>ABS(G$3-I76)</f>
+        <v>0.3571428571428571</v>
+      </c>
+      <c r="K76" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.3571428571428571</v>
+      </c>
+      <c r="M76" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N76" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P76" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q76" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R76" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="S76" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B77" s="4"/>
-      <c r="I77" s="3"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="5"/>
-      <c r="M77" s="4"/>
+      <c r="B77" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C77" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F77" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G77" s="1">
+        <v>15</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J77" s="13">
+        <f>ABS(G$3-I77)</f>
+        <v>1</v>
+      </c>
+      <c r="K77" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M77" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N77" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P77" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q77" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R77" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S77" s="1">
+        <v>90</v>
+      </c>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B78" s="4"/>
-      <c r="I78" s="3"/>
-      <c r="J78" s="1"/>
-      <c r="K78" s="5"/>
-      <c r="M78" s="4"/>
+      <c r="B78" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C78" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E78" s="1">
+        <v>100</v>
+      </c>
+      <c r="F78" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G78" s="1">
+        <v>103</v>
+      </c>
+      <c r="H78" s="1">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J78" s="13">
+        <f t="shared" ref="J78:J82" si="10">ABS(G$3-I78)</f>
+        <v>1</v>
+      </c>
+      <c r="K78" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M78" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N78" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P78" s="1">
+        <v>800</v>
+      </c>
+      <c r="Q78" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R78" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="S78" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B79" s="4"/>
-      <c r="I79" s="3"/>
-      <c r="J79" s="1"/>
-      <c r="K79" s="5"/>
-      <c r="M79" s="4"/>
+      <c r="B79" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C79" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E79" s="1">
+        <v>200</v>
+      </c>
+      <c r="F79" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G79" s="1">
+        <v>103</v>
+      </c>
+      <c r="H79" s="1">
+        <v>15</v>
+      </c>
+      <c r="I79" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.14563106796116504</v>
+      </c>
+      <c r="J79" s="13">
+        <f t="shared" si="10"/>
+        <v>0.85436893203883502</v>
+      </c>
+      <c r="K79" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.85436893203883502</v>
+      </c>
+      <c r="M79" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N79" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P79" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q79" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R79" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="S79" s="1">
+        <v>69</v>
+      </c>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B80" s="4"/>
-      <c r="I80" s="3"/>
-      <c r="J80" s="1"/>
-      <c r="K80" s="5"/>
-      <c r="M80" s="4"/>
-    </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B81" s="4"/>
-      <c r="I81" s="3"/>
-      <c r="J81" s="1"/>
-      <c r="K81" s="5"/>
-      <c r="M81" s="4"/>
-    </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B82" s="4"/>
-      <c r="I82" s="3"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="5"/>
-      <c r="M82" s="4"/>
-    </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B83" s="4"/>
-      <c r="I83" s="3"/>
-      <c r="J83" s="1"/>
-      <c r="K83" s="5"/>
-      <c r="M83" s="4"/>
-    </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B84" s="4"/>
-      <c r="I84" s="3"/>
-      <c r="J84" s="1"/>
-      <c r="K84" s="5"/>
-      <c r="M84" s="4"/>
-    </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B85" s="4"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="1"/>
-      <c r="K85" s="5"/>
+      <c r="B80" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C80" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E80" s="1">
+        <v>300</v>
+      </c>
+      <c r="F80" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G80" s="1">
+        <v>103</v>
+      </c>
+      <c r="H80" s="1">
+        <v>3</v>
+      </c>
+      <c r="I80" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>2.9126213592233011E-2</v>
+      </c>
+      <c r="J80" s="13">
+        <f t="shared" si="10"/>
+        <v>0.970873786407767</v>
+      </c>
+      <c r="K80" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.970873786407767</v>
+      </c>
+      <c r="M80" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N80" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P80" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q80" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R80" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="S80" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B81" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C81" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E81" s="1">
+        <v>400</v>
+      </c>
+      <c r="F81" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G81" s="1">
+        <v>103</v>
+      </c>
+      <c r="H81" s="1">
+        <v>2</v>
+      </c>
+      <c r="I81" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>1.9417475728155338E-2</v>
+      </c>
+      <c r="J81" s="13">
+        <f t="shared" si="10"/>
+        <v>0.98058252427184467</v>
+      </c>
+      <c r="K81" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.98058252427184467</v>
+      </c>
+      <c r="M81" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N81" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O81" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P81" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q81" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R81" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S81" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B82" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C82" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E82" s="1">
+        <v>500</v>
+      </c>
+      <c r="F82" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G82" s="1">
+        <v>103</v>
+      </c>
+      <c r="H82" s="1">
+        <v>0</v>
+      </c>
+      <c r="I82" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J82" s="13">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="K82" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M82" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N82" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P82" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q82" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R82" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="S82" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B83" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C83" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E83" s="1">
+        <v>600</v>
+      </c>
+      <c r="F83" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G83" s="1">
+        <v>101</v>
+      </c>
+      <c r="H83" s="1">
+        <v>80</v>
+      </c>
+      <c r="I83" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.79207920792079212</v>
+      </c>
+      <c r="J83" s="13">
+        <f t="shared" ref="J83:J89" si="11">ABS(G$3-I83)</f>
+        <v>0.20792079207920788</v>
+      </c>
+      <c r="K83" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.20792079207920788</v>
+      </c>
+      <c r="M83" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N83" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P83" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q83" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R83" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S83" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B84" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C84" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E84" s="1">
+        <v>700</v>
+      </c>
+      <c r="F84" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G84" s="1">
+        <v>101</v>
+      </c>
+      <c r="H84" s="1">
+        <v>90</v>
+      </c>
+      <c r="I84" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.8910891089108911</v>
+      </c>
+      <c r="J84" s="13">
+        <f t="shared" si="11"/>
+        <v>0.1089108910891089</v>
+      </c>
+      <c r="K84" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.1089108910891089</v>
+      </c>
+      <c r="M84" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N84" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O84" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P84" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q84" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R84" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="S84" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B85" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C85" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E85" s="1">
+        <v>800</v>
+      </c>
+      <c r="F85" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G85" s="1">
+        <v>101</v>
+      </c>
+      <c r="H85" s="1">
+        <v>3</v>
+      </c>
+      <c r="I85" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>2.9702970297029702E-2</v>
+      </c>
+      <c r="J85" s="13">
+        <f t="shared" si="11"/>
+        <v>0.97029702970297027</v>
+      </c>
+      <c r="K85" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.97029702970297027</v>
+      </c>
       <c r="M85" s="4"/>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B86" s="4"/>
-      <c r="I86" s="3"/>
-      <c r="J86" s="1"/>
-      <c r="K86" s="5"/>
+    <row r="86" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B86" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C86" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F86" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G86" s="1">
+        <v>100</v>
+      </c>
+      <c r="H86" s="1">
+        <v>69</v>
+      </c>
+      <c r="I86" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.69</v>
+      </c>
+      <c r="J86" s="13">
+        <f t="shared" si="11"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="K86" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.31000000000000005</v>
+      </c>
       <c r="M86" s="4"/>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B87" s="4"/>
-      <c r="I87" s="3"/>
-      <c r="J87" s="1"/>
-      <c r="K87" s="5"/>
+    <row r="87" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B87" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C87" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F87" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G87" s="1">
+        <v>86</v>
+      </c>
+      <c r="H87" s="1">
+        <v>14</v>
+      </c>
+      <c r="I87" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.16279069767441862</v>
+      </c>
+      <c r="J87" s="13">
+        <f t="shared" si="11"/>
+        <v>0.83720930232558133</v>
+      </c>
+      <c r="K87" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.83720930232558133</v>
+      </c>
       <c r="M87" s="4"/>
     </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B88" s="4"/>
-      <c r="I88" s="3"/>
-      <c r="J88" s="1"/>
-      <c r="K88" s="5"/>
+    <row r="88" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B88" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C88" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F88" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G88" s="1">
+        <v>83</v>
+      </c>
+      <c r="H88" s="1">
+        <v>17</v>
+      </c>
+      <c r="I88" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.20481927710843373</v>
+      </c>
+      <c r="J88" s="13">
+        <f>ABS(G$3-I88)</f>
+        <v>0.79518072289156627</v>
+      </c>
+      <c r="K88" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.79518072289156627</v>
+      </c>
       <c r="M88" s="4"/>
     </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B89" s="4"/>
-      <c r="I89" s="3"/>
-      <c r="J89" s="1"/>
-      <c r="K89" s="5"/>
+    <row r="89" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B89" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C89" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F89" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G89" s="1">
+        <v>45</v>
+      </c>
+      <c r="H89" s="1">
+        <v>7</v>
+      </c>
+      <c r="I89" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.15555555555555556</v>
+      </c>
+      <c r="J89" s="13">
+        <f t="shared" si="11"/>
+        <v>0.84444444444444444</v>
+      </c>
+      <c r="K89" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.84444444444444444</v>
+      </c>
       <c r="M89" s="4"/>
     </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B90" s="4"/>
-      <c r="I90" s="3"/>
-      <c r="J90" s="1"/>
-      <c r="K90" s="5"/>
+    <row r="90" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B90" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C90" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F90" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G90" s="1">
+        <v>33</v>
+      </c>
+      <c r="H90" s="1">
+        <v>7</v>
+      </c>
+      <c r="I90" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.21212121212121213</v>
+      </c>
+      <c r="J90" s="13">
+        <f>ABS(G$3-I90)</f>
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="K90" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.78787878787878785</v>
+      </c>
       <c r="M90" s="4"/>
     </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B91" s="4"/>
       <c r="I91" s="3"/>
       <c r="J91" s="1"/>
       <c r="K91" s="5"/>
       <c r="M91" s="4"/>
     </row>
-    <row r="92" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B92" s="4"/>
       <c r="I92" s="3"/>
       <c r="J92" s="1"/>
       <c r="K92" s="5"/>
       <c r="M92" s="4"/>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B93" s="4"/>
       <c r="I93" s="3"/>
       <c r="J93" s="1"/>
       <c r="K93" s="5"/>
       <c r="M93" s="4"/>
     </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B94" s="4"/>
       <c r="I94" s="3"/>
       <c r="J94" s="1"/>
       <c r="K94" s="5"/>
       <c r="M94" s="4"/>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B95" s="4"/>
       <c r="I95" s="3"/>
       <c r="J95" s="1"/>
       <c r="K95" s="5"/>
       <c r="M95" s="4"/>
     </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B96" s="4"/>
       <c r="I96" s="3"/>
       <c r="J96" s="1"/>
@@ -29415,6 +30581,8 @@
       <c r="J215" s="1"/>
       <c r="K215" s="5"/>
       <c r="M215" s="4"/>
+      <c r="U215" s="1"/>
+      <c r="V215" s="1"/>
     </row>
     <row r="216" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B216" s="4"/>
@@ -29422,6 +30590,8 @@
       <c r="J216" s="1"/>
       <c r="K216" s="5"/>
       <c r="M216" s="4"/>
+      <c r="U216" s="1"/>
+      <c r="V216" s="1"/>
     </row>
     <row r="217" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B217" s="4"/>
@@ -29443,8 +30613,6 @@
       <c r="J219" s="1"/>
       <c r="K219" s="5"/>
       <c r="M219" s="4"/>
-      <c r="U219" s="1"/>
-      <c r="V219" s="1"/>
     </row>
     <row r="220" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B220" s="4"/>
@@ -29452,8 +30620,6 @@
       <c r="J220" s="1"/>
       <c r="K220" s="5"/>
       <c r="M220" s="4"/>
-      <c r="U220" s="1"/>
-      <c r="V220" s="1"/>
     </row>
     <row r="221" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B221" s="4"/>
@@ -29537,21 +30703,21 @@
       <c r="I232" s="3"/>
       <c r="J232" s="1"/>
       <c r="K232" s="5"/>
-      <c r="M232" s="4"/>
+      <c r="M232" s="8"/>
     </row>
     <row r="233" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B233" s="4"/>
       <c r="I233" s="3"/>
       <c r="J233" s="1"/>
       <c r="K233" s="5"/>
-      <c r="M233" s="4"/>
+      <c r="M233" s="8"/>
     </row>
     <row r="234" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B234" s="4"/>
       <c r="I234" s="3"/>
       <c r="J234" s="1"/>
       <c r="K234" s="5"/>
-      <c r="M234" s="4"/>
+      <c r="M234" s="8"/>
     </row>
     <row r="235" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B235" s="4"/>
@@ -29565,21 +30731,21 @@
       <c r="I236" s="3"/>
       <c r="J236" s="1"/>
       <c r="K236" s="5"/>
-      <c r="M236" s="8"/>
+      <c r="M236" s="4"/>
     </row>
     <row r="237" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B237" s="4"/>
       <c r="I237" s="3"/>
       <c r="J237" s="1"/>
       <c r="K237" s="5"/>
-      <c r="M237" s="8"/>
+      <c r="M237" s="4"/>
     </row>
     <row r="238" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B238" s="4"/>
       <c r="I238" s="3"/>
       <c r="J238" s="1"/>
       <c r="K238" s="5"/>
-      <c r="M238" s="8"/>
+      <c r="M238" s="4"/>
     </row>
     <row r="239" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B239" s="4"/>
@@ -29844,53 +31010,45 @@
       <c r="B276" s="4"/>
       <c r="I276" s="3"/>
       <c r="J276" s="1"/>
-      <c r="K276" s="5"/>
       <c r="M276" s="4"/>
     </row>
     <row r="277" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B277" s="4"/>
       <c r="I277" s="3"/>
       <c r="J277" s="1"/>
-      <c r="K277" s="5"/>
       <c r="M277" s="4"/>
     </row>
     <row r="278" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B278" s="4"/>
       <c r="I278" s="3"/>
       <c r="J278" s="1"/>
-      <c r="K278" s="5"/>
       <c r="M278" s="4"/>
     </row>
     <row r="279" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B279" s="4"/>
       <c r="I279" s="3"/>
       <c r="J279" s="1"/>
-      <c r="K279" s="5"/>
       <c r="M279" s="4"/>
     </row>
     <row r="280" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B280" s="4"/>
       <c r="I280" s="3"/>
       <c r="J280" s="1"/>
-      <c r="M280" s="4"/>
     </row>
     <row r="281" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B281" s="4"/>
       <c r="I281" s="3"/>
       <c r="J281" s="1"/>
-      <c r="M281" s="4"/>
     </row>
     <row r="282" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B282" s="4"/>
       <c r="I282" s="3"/>
       <c r="J282" s="1"/>
-      <c r="M282" s="4"/>
     </row>
     <row r="283" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B283" s="4"/>
       <c r="I283" s="3"/>
       <c r="J283" s="1"/>
-      <c r="M283" s="4"/>
     </row>
     <row r="284" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B284" s="4"/>
@@ -29963,6 +31121,9 @@
       <c r="J297" s="1"/>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>0</v>
+      </c>
       <c r="B298" s="4"/>
       <c r="I298" s="3"/>
       <c r="J298" s="1"/>
@@ -29983,9 +31144,6 @@
       <c r="J301" s="1"/>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A302" t="s">
-        <v>0</v>
-      </c>
       <c r="B302" s="4"/>
       <c r="I302" s="3"/>
       <c r="J302" s="1"/>
@@ -30166,6 +31324,9 @@
       <c r="J337" s="1"/>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>0</v>
+      </c>
       <c r="B338" s="4"/>
       <c r="I338" s="3"/>
       <c r="J338" s="1"/>
@@ -30186,9 +31347,6 @@
       <c r="J341" s="1"/>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A342" t="s">
-        <v>0</v>
-      </c>
       <c r="B342" s="4"/>
       <c r="I342" s="3"/>
       <c r="J342" s="1"/>
@@ -30592,21 +31750,33 @@
       <c r="B422" s="4"/>
       <c r="I422" s="3"/>
       <c r="J422" s="1"/>
+      <c r="M422" s="7"/>
+      <c r="N422" s="7"/>
+      <c r="O422" s="7"/>
     </row>
     <row r="423" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B423" s="4"/>
       <c r="I423" s="3"/>
       <c r="J423" s="1"/>
+      <c r="M423" s="7"/>
+      <c r="N423" s="7"/>
+      <c r="O423" s="7"/>
     </row>
     <row r="424" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B424" s="4"/>
       <c r="I424" s="3"/>
       <c r="J424" s="1"/>
+      <c r="M424" s="7"/>
+      <c r="N424" s="7"/>
+      <c r="O424" s="7"/>
     </row>
     <row r="425" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B425" s="4"/>
       <c r="I425" s="3"/>
       <c r="J425" s="1"/>
+      <c r="M425" s="7"/>
+      <c r="N425" s="7"/>
+      <c r="O425" s="7"/>
     </row>
     <row r="426" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B426" s="4"/>
@@ -30733,7 +31903,7 @@
       <c r="I441" s="3"/>
       <c r="J441" s="1"/>
       <c r="M441" s="7"/>
-      <c r="N441" s="7"/>
+      <c r="N441" s="8"/>
       <c r="O441" s="7"/>
     </row>
     <row r="442" spans="2:15" x14ac:dyDescent="0.3">
@@ -30765,7 +31935,7 @@
       <c r="I445" s="3"/>
       <c r="J445" s="1"/>
       <c r="M445" s="7"/>
-      <c r="N445" s="8"/>
+      <c r="N445" s="7"/>
       <c r="O445" s="7"/>
     </row>
     <row r="446" spans="2:15" x14ac:dyDescent="0.3">
@@ -30964,33 +32134,21 @@
       <c r="B470" s="4"/>
       <c r="I470" s="3"/>
       <c r="J470" s="1"/>
-      <c r="M470" s="7"/>
-      <c r="N470" s="7"/>
-      <c r="O470" s="7"/>
     </row>
     <row r="471" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B471" s="4"/>
       <c r="I471" s="3"/>
       <c r="J471" s="1"/>
-      <c r="M471" s="7"/>
-      <c r="N471" s="7"/>
-      <c r="O471" s="7"/>
     </row>
     <row r="472" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B472" s="4"/>
       <c r="I472" s="3"/>
       <c r="J472" s="1"/>
-      <c r="M472" s="7"/>
-      <c r="N472" s="7"/>
-      <c r="O472" s="7"/>
     </row>
     <row r="473" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B473" s="4"/>
       <c r="I473" s="3"/>
       <c r="J473" s="1"/>
-      <c r="M473" s="7"/>
-      <c r="N473" s="7"/>
-      <c r="O473" s="7"/>
     </row>
     <row r="474" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B474" s="4"/>
@@ -32008,6 +33166,9 @@
       <c r="J676" s="1"/>
     </row>
     <row r="677" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A677" t="s">
+        <v>0</v>
+      </c>
       <c r="B677" s="4"/>
       <c r="I677" s="3"/>
       <c r="J677" s="1"/>
@@ -32028,9 +33189,6 @@
       <c r="J680" s="1"/>
     </row>
     <row r="681" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A681" t="s">
-        <v>0</v>
-      </c>
       <c r="B681" s="4"/>
       <c r="I681" s="3"/>
       <c r="J681" s="1"/>
@@ -32041,6 +33199,9 @@
       <c r="J682" s="1"/>
     </row>
     <row r="683" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A683" t="s">
+        <v>0</v>
+      </c>
       <c r="B683" s="4"/>
       <c r="I683" s="3"/>
       <c r="J683" s="1"/>
@@ -32061,9 +33222,6 @@
       <c r="J686" s="1"/>
     </row>
     <row r="687" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A687" t="s">
-        <v>0</v>
-      </c>
       <c r="B687" s="4"/>
       <c r="I687" s="3"/>
       <c r="J687" s="1"/>
@@ -32074,6 +33232,9 @@
       <c r="J688" s="1"/>
     </row>
     <row r="689" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A689" t="s">
+        <v>0</v>
+      </c>
       <c r="B689" s="4"/>
       <c r="I689" s="3"/>
       <c r="J689" s="1"/>
@@ -32094,9 +33255,6 @@
       <c r="J692" s="1"/>
     </row>
     <row r="693" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A693" t="s">
-        <v>0</v>
-      </c>
       <c r="B693" s="4"/>
       <c r="I693" s="3"/>
       <c r="J693" s="1"/>
@@ -32107,6 +33265,9 @@
       <c r="J694" s="1"/>
     </row>
     <row r="695" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A695" t="s">
+        <v>0</v>
+      </c>
       <c r="B695" s="4"/>
       <c r="I695" s="3"/>
       <c r="J695" s="1"/>
@@ -32127,9 +33288,6 @@
       <c r="J698" s="1"/>
     </row>
     <row r="699" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A699" t="s">
-        <v>0</v>
-      </c>
       <c r="B699" s="4"/>
       <c r="I699" s="3"/>
       <c r="J699" s="1"/>
@@ -32140,6 +33298,9 @@
       <c r="J700" s="1"/>
     </row>
     <row r="701" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A701" t="s">
+        <v>0</v>
+      </c>
       <c r="B701" s="4"/>
       <c r="I701" s="3"/>
       <c r="J701" s="1"/>
@@ -32160,9 +33321,6 @@
       <c r="J704" s="1"/>
     </row>
     <row r="705" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A705" t="s">
-        <v>0</v>
-      </c>
       <c r="B705" s="4"/>
       <c r="I705" s="3"/>
       <c r="J705" s="1"/>
@@ -32173,6 +33331,9 @@
       <c r="J706" s="1"/>
     </row>
     <row r="707" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A707" t="s">
+        <v>0</v>
+      </c>
       <c r="B707" s="4"/>
       <c r="I707" s="3"/>
       <c r="J707" s="1"/>
@@ -32193,9 +33354,6 @@
       <c r="J710" s="1"/>
     </row>
     <row r="711" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A711" t="s">
-        <v>0</v>
-      </c>
       <c r="B711" s="4"/>
       <c r="I711" s="3"/>
       <c r="J711" s="1"/>
@@ -32296,6 +33454,9 @@
       <c r="J730" s="1"/>
     </row>
     <row r="731" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A731" t="s">
+        <v>0</v>
+      </c>
       <c r="B731" s="4"/>
       <c r="I731" s="3"/>
       <c r="J731" s="1"/>
@@ -32316,9 +33477,6 @@
       <c r="J734" s="1"/>
     </row>
     <row r="735" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A735" t="s">
-        <v>0</v>
-      </c>
       <c r="B735" s="4"/>
       <c r="I735" s="3"/>
       <c r="J735" s="1"/>
@@ -32328,165 +33486,165 @@
       <c r="I736" s="3"/>
       <c r="J736" s="1"/>
     </row>
-    <row r="737" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B737" s="4"/>
       <c r="I737" s="3"/>
       <c r="J737" s="1"/>
     </row>
-    <row r="738" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B738" s="4"/>
       <c r="I738" s="3"/>
       <c r="J738" s="1"/>
     </row>
-    <row r="739" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B739" s="4"/>
       <c r="I739" s="3"/>
       <c r="J739" s="1"/>
     </row>
-    <row r="740" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B740" s="4"/>
       <c r="I740" s="3"/>
       <c r="J740" s="1"/>
     </row>
-    <row r="741" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B741" s="4"/>
       <c r="I741" s="3"/>
       <c r="J741" s="1"/>
     </row>
-    <row r="742" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B742" s="4"/>
       <c r="I742" s="3"/>
       <c r="J742" s="1"/>
     </row>
-    <row r="743" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B743" s="4"/>
       <c r="I743" s="3"/>
       <c r="J743" s="1"/>
     </row>
-    <row r="744" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B744" s="4"/>
       <c r="I744" s="3"/>
       <c r="J744" s="1"/>
     </row>
-    <row r="745" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B745" s="4"/>
       <c r="I745" s="3"/>
       <c r="J745" s="1"/>
     </row>
-    <row r="746" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B746" s="4"/>
       <c r="I746" s="3"/>
       <c r="J746" s="1"/>
     </row>
-    <row r="747" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B747" s="4"/>
       <c r="I747" s="3"/>
       <c r="J747" s="1"/>
     </row>
-    <row r="748" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B748" s="4"/>
       <c r="I748" s="3"/>
       <c r="J748" s="1"/>
     </row>
-    <row r="749" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A749" t="s">
+        <v>0</v>
+      </c>
       <c r="B749" s="4"/>
       <c r="I749" s="3"/>
       <c r="J749" s="1"/>
     </row>
-    <row r="750" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B750" s="4"/>
       <c r="I750" s="3"/>
       <c r="J750" s="1"/>
     </row>
-    <row r="751" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B751" s="4"/>
       <c r="I751" s="3"/>
       <c r="J751" s="1"/>
     </row>
-    <row r="752" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B752" s="4"/>
       <c r="I752" s="3"/>
       <c r="J752" s="1"/>
     </row>
-    <row r="753" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A753" t="s">
-        <v>0</v>
-      </c>
+    <row r="753" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B753" s="4"/>
       <c r="I753" s="3"/>
       <c r="J753" s="1"/>
     </row>
-    <row r="754" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="754" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B754" s="4"/>
       <c r="I754" s="3"/>
       <c r="J754" s="1"/>
     </row>
-    <row r="755" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="755" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B755" s="4"/>
       <c r="I755" s="3"/>
       <c r="J755" s="1"/>
     </row>
-    <row r="756" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="756" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B756" s="4"/>
       <c r="I756" s="3"/>
       <c r="J756" s="1"/>
     </row>
-    <row r="757" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="757" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B757" s="4"/>
       <c r="I757" s="3"/>
       <c r="J757" s="1"/>
     </row>
-    <row r="758" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="758" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B758" s="4"/>
       <c r="I758" s="3"/>
       <c r="J758" s="1"/>
     </row>
-    <row r="759" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="759" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B759" s="4"/>
       <c r="I759" s="3"/>
       <c r="J759" s="1"/>
     </row>
-    <row r="760" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="760" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B760" s="4"/>
       <c r="I760" s="3"/>
       <c r="J760" s="1"/>
     </row>
-    <row r="761" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="761" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B761" s="4"/>
       <c r="I761" s="3"/>
       <c r="J761" s="1"/>
     </row>
-    <row r="762" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="762" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B762" s="4"/>
       <c r="I762" s="3"/>
       <c r="J762" s="1"/>
     </row>
-    <row r="763" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="763" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B763" s="4"/>
       <c r="I763" s="3"/>
       <c r="J763" s="1"/>
     </row>
-    <row r="764" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="764" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B764" s="4"/>
       <c r="I764" s="3"/>
       <c r="J764" s="1"/>
     </row>
-    <row r="765" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="765" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B765" s="4"/>
       <c r="I765" s="3"/>
       <c r="J765" s="1"/>
     </row>
-    <row r="766" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="766" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B766" s="4"/>
       <c r="I766" s="3"/>
       <c r="J766" s="1"/>
     </row>
-    <row r="767" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="767" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B767" s="4"/>
       <c r="I767" s="3"/>
       <c r="J767" s="1"/>
     </row>
-    <row r="768" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="768" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B768" s="4"/>
       <c r="I768" s="3"/>
       <c r="J768" s="1"/>
@@ -32572,7 +33730,6 @@
       <c r="J784" s="1"/>
     </row>
     <row r="785" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B785" s="4"/>
       <c r="I785" s="3"/>
       <c r="J785" s="1"/>
     </row>
@@ -32592,6 +33749,7 @@
       <c r="J788" s="1"/>
     </row>
     <row r="789" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B789" s="4"/>
       <c r="I789" s="3"/>
       <c r="J789" s="1"/>
     </row>
@@ -32632,6 +33790,7 @@
     </row>
     <row r="797" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B797" s="4"/>
+      <c r="G797" s="4"/>
       <c r="I797" s="3"/>
       <c r="J797" s="1"/>
     </row>
@@ -32652,7 +33811,6 @@
     </row>
     <row r="801" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B801" s="4"/>
-      <c r="G801" s="4"/>
       <c r="I801" s="3"/>
       <c r="J801" s="1"/>
     </row>
@@ -32770,26 +33928,6 @@
       <c r="B824" s="4"/>
       <c r="I824" s="3"/>
       <c r="J824" s="1"/>
-    </row>
-    <row r="825" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B825" s="4"/>
-      <c r="I825" s="3"/>
-      <c r="J825" s="1"/>
-    </row>
-    <row r="826" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B826" s="4"/>
-      <c r="I826" s="3"/>
-      <c r="J826" s="1"/>
-    </row>
-    <row r="827" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B827" s="4"/>
-      <c r="I827" s="3"/>
-      <c r="J827" s="1"/>
-    </row>
-    <row r="828" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B828" s="4"/>
-      <c r="I828" s="3"/>
-      <c r="J828" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\5_MB MMA\09_Information\10_FTQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D44759-09D7-4A13-BF59-33E41A7C989E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37415832-24D7-4459-BC2D-E251FB0DFDD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE DE DATOS" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$98</definedName>
     <definedName name="DATA_01">[1]Data_Lineal!$H$4:$Y$30</definedName>
     <definedName name="DB_01">#REF!</definedName>
     <definedName name="DB_CAP01">'[2]CAPACIDAD (1)'!$X$9:$AM$29</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="85">
   <si>
     <t>*</t>
   </si>
@@ -308,6 +308,18 @@
   <si>
     <t>Falla 4000.130 Op.Calibrador SAS2</t>
   </si>
+  <si>
+    <t>Falla de inspección visual en resortes sin NG Op.100</t>
+  </si>
+  <si>
+    <t>Mala colocación del engrane grande Op.200</t>
+  </si>
+  <si>
+    <t>Mal ensamble de elemento de compensación en rodamiento Op.400</t>
+  </si>
+  <si>
+    <t>No ensambla tornillo</t>
+  </si>
 </sst>
 </file>
 
@@ -388,7 +400,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -423,6 +435,9 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -432,7 +447,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="21">
     <dxf>
@@ -24414,7 +24429,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K90" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K98" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CDAA4D20-2955-41E2-BD7E-9330E166FFF4}" name="Fecha" dataDxfId="18"/>
     <tableColumn id="9" xr3:uid="{F70BB124-92DE-4024-874C-EE3BA966CDE6}" name="Semana" dataDxfId="17">
@@ -24440,7 +24455,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S84" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S95" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="07/09/2026" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="37" dataDxfId="5">
@@ -24721,7 +24736,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A1B645-8848-474A-88BA-FA9209B01B4F}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:V824"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
     <col min="2" max="2" width="13.21875" style="1" customWidth="1"/>
@@ -24743,46 +24758,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
       <c r="K1" s="6"/>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
     </row>
     <row r="2" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
       <c r="K2" s="6"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.3">
       <c r="G3" s="1">
@@ -24826,7 +24841,7 @@
       <c r="M4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="N4" s="1" t="s">
         <v>71</v>
       </c>
       <c r="O4" s="1" t="s">
@@ -28445,7 +28460,7 @@
       <c r="B67" s="4">
         <v>46269</v>
       </c>
-      <c r="C67" s="13">
+      <c r="C67" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
@@ -28468,7 +28483,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J67" s="13">
+      <c r="J67" s="1">
         <f t="shared" ref="J67:J75" si="9">ABS(G$3-I67)</f>
         <v>1</v>
       </c>
@@ -28479,7 +28494,7 @@
       <c r="M67" s="4">
         <v>46269</v>
       </c>
-      <c r="N67" s="13">
+      <c r="N67" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>36</v>
       </c>
@@ -28503,7 +28518,7 @@
       <c r="B68" s="4">
         <v>46269</v>
       </c>
-      <c r="C68" s="13">
+      <c r="C68" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
@@ -28526,7 +28541,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J68" s="13">
+      <c r="J68" s="1">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -28537,7 +28552,7 @@
       <c r="M68" s="4">
         <v>46269</v>
       </c>
-      <c r="N68" s="13">
+      <c r="N68" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>36</v>
       </c>
@@ -28561,7 +28576,7 @@
       <c r="B69" s="4">
         <v>46269</v>
       </c>
-      <c r="C69" s="13">
+      <c r="C69" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
@@ -28584,7 +28599,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J69" s="13">
+      <c r="J69" s="1">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -28595,7 +28610,7 @@
       <c r="M69" s="4">
         <v>46269</v>
       </c>
-      <c r="N69" s="13">
+      <c r="N69" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>36</v>
       </c>
@@ -28619,7 +28634,7 @@
       <c r="B70" s="4">
         <v>46269</v>
       </c>
-      <c r="C70" s="13">
+      <c r="C70" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
@@ -28642,7 +28657,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.4</v>
       </c>
-      <c r="J70" s="13">
+      <c r="J70" s="1">
         <f t="shared" si="9"/>
         <v>0.6</v>
       </c>
@@ -28653,7 +28668,7 @@
       <c r="M70" s="4">
         <v>46269</v>
       </c>
-      <c r="N70" s="13">
+      <c r="N70" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>36</v>
       </c>
@@ -28677,7 +28692,7 @@
       <c r="B71" s="4">
         <v>46269</v>
       </c>
-      <c r="C71" s="13">
+      <c r="C71" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
@@ -28700,7 +28715,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J71" s="13">
+      <c r="J71" s="1">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -28711,7 +28726,7 @@
       <c r="M71" s="4">
         <v>46272</v>
       </c>
-      <c r="N71" s="13">
+      <c r="N71" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>37</v>
       </c>
@@ -28735,7 +28750,7 @@
       <c r="B72" s="4">
         <v>46269</v>
       </c>
-      <c r="C72" s="13">
+      <c r="C72" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
@@ -28758,7 +28773,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.4</v>
       </c>
-      <c r="J72" s="13">
+      <c r="J72" s="1">
         <f t="shared" si="9"/>
         <v>0.6</v>
       </c>
@@ -28769,7 +28784,7 @@
       <c r="M72" s="4">
         <v>46272</v>
       </c>
-      <c r="N72" s="13">
+      <c r="N72" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>37</v>
       </c>
@@ -28793,7 +28808,7 @@
       <c r="B73" s="4">
         <v>46269</v>
       </c>
-      <c r="C73" s="13">
+      <c r="C73" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
@@ -28816,7 +28831,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J73" s="13">
+      <c r="J73" s="1">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -28827,7 +28842,7 @@
       <c r="M73" s="4">
         <v>46272</v>
       </c>
-      <c r="N73" s="13">
+      <c r="N73" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>37</v>
       </c>
@@ -28851,7 +28866,7 @@
       <c r="B74" s="4">
         <v>46269</v>
       </c>
-      <c r="C74" s="13">
+      <c r="C74" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
@@ -28874,7 +28889,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J74" s="13">
+      <c r="J74" s="1">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -28885,7 +28900,7 @@
       <c r="M74" s="4">
         <v>46272</v>
       </c>
-      <c r="N74" s="13">
+      <c r="N74" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>37</v>
       </c>
@@ -28909,7 +28924,7 @@
       <c r="B75" s="4">
         <v>46269</v>
       </c>
-      <c r="C75" s="13">
+      <c r="C75" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
@@ -28932,7 +28947,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J75" s="13">
+      <c r="J75" s="1">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -28943,7 +28958,7 @@
       <c r="M75" s="4">
         <v>46272</v>
       </c>
-      <c r="N75" s="13">
+      <c r="N75" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>37</v>
       </c>
@@ -28967,7 +28982,7 @@
       <c r="B76" s="4">
         <v>46269</v>
       </c>
-      <c r="C76" s="13">
+      <c r="C76" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
@@ -28990,7 +29005,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.6428571428571429</v>
       </c>
-      <c r="J76" s="13">
+      <c r="J76" s="1">
         <f>ABS(G$3-I76)</f>
         <v>0.3571428571428571</v>
       </c>
@@ -29001,7 +29016,7 @@
       <c r="M76" s="4">
         <v>46272</v>
       </c>
-      <c r="N76" s="13">
+      <c r="N76" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>37</v>
       </c>
@@ -29025,7 +29040,7 @@
       <c r="B77" s="4">
         <v>46269</v>
       </c>
-      <c r="C77" s="13">
+      <c r="C77" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
@@ -29048,7 +29063,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J77" s="13">
+      <c r="J77" s="1">
         <f>ABS(G$3-I77)</f>
         <v>1</v>
       </c>
@@ -29059,7 +29074,7 @@
       <c r="M77" s="4">
         <v>46272</v>
       </c>
-      <c r="N77" s="13">
+      <c r="N77" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>37</v>
       </c>
@@ -29083,7 +29098,7 @@
       <c r="B78" s="4">
         <v>46272</v>
       </c>
-      <c r="C78" s="13">
+      <c r="C78" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>37</v>
       </c>
@@ -29106,7 +29121,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J78" s="13">
+      <c r="J78" s="1">
         <f t="shared" ref="J78:J82" si="10">ABS(G$3-I78)</f>
         <v>1</v>
       </c>
@@ -29117,7 +29132,7 @@
       <c r="M78" s="4">
         <v>46272</v>
       </c>
-      <c r="N78" s="13">
+      <c r="N78" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>37</v>
       </c>
@@ -29141,7 +29156,7 @@
       <c r="B79" s="4">
         <v>46272</v>
       </c>
-      <c r="C79" s="13">
+      <c r="C79" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>37</v>
       </c>
@@ -29164,7 +29179,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.14563106796116504</v>
       </c>
-      <c r="J79" s="13">
+      <c r="J79" s="1">
         <f t="shared" si="10"/>
         <v>0.85436893203883502</v>
       </c>
@@ -29175,7 +29190,7 @@
       <c r="M79" s="4">
         <v>46272</v>
       </c>
-      <c r="N79" s="13">
+      <c r="N79" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>37</v>
       </c>
@@ -29199,7 +29214,7 @@
       <c r="B80" s="4">
         <v>46272</v>
       </c>
-      <c r="C80" s="13">
+      <c r="C80" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>37</v>
       </c>
@@ -29222,7 +29237,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>2.9126213592233011E-2</v>
       </c>
-      <c r="J80" s="13">
+      <c r="J80" s="1">
         <f t="shared" si="10"/>
         <v>0.970873786407767</v>
       </c>
@@ -29233,7 +29248,7 @@
       <c r="M80" s="4">
         <v>46272</v>
       </c>
-      <c r="N80" s="13">
+      <c r="N80" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>37</v>
       </c>
@@ -29257,7 +29272,7 @@
       <c r="B81" s="4">
         <v>46272</v>
       </c>
-      <c r="C81" s="13">
+      <c r="C81" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>37</v>
       </c>
@@ -29280,7 +29295,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>1.9417475728155338E-2</v>
       </c>
-      <c r="J81" s="13">
+      <c r="J81" s="1">
         <f t="shared" si="10"/>
         <v>0.98058252427184467</v>
       </c>
@@ -29291,7 +29306,7 @@
       <c r="M81" s="4">
         <v>46272</v>
       </c>
-      <c r="N81" s="13">
+      <c r="N81" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>37</v>
       </c>
@@ -29315,7 +29330,7 @@
       <c r="B82" s="4">
         <v>46272</v>
       </c>
-      <c r="C82" s="13">
+      <c r="C82" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>37</v>
       </c>
@@ -29338,7 +29353,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J82" s="13">
+      <c r="J82" s="1">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -29349,7 +29364,7 @@
       <c r="M82" s="4">
         <v>46272</v>
       </c>
-      <c r="N82" s="13">
+      <c r="N82" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>37</v>
       </c>
@@ -29373,7 +29388,7 @@
       <c r="B83" s="4">
         <v>46272</v>
       </c>
-      <c r="C83" s="13">
+      <c r="C83" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>37</v>
       </c>
@@ -29396,7 +29411,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.79207920792079212</v>
       </c>
-      <c r="J83" s="13">
+      <c r="J83" s="1">
         <f t="shared" ref="J83:J89" si="11">ABS(G$3-I83)</f>
         <v>0.20792079207920788</v>
       </c>
@@ -29407,7 +29422,7 @@
       <c r="M83" s="4">
         <v>46272</v>
       </c>
-      <c r="N83" s="13">
+      <c r="N83" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>37</v>
       </c>
@@ -29431,7 +29446,7 @@
       <c r="B84" s="4">
         <v>46272</v>
       </c>
-      <c r="C84" s="13">
+      <c r="C84" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>37</v>
       </c>
@@ -29454,7 +29469,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.8910891089108911</v>
       </c>
-      <c r="J84" s="13">
+      <c r="J84" s="1">
         <f t="shared" si="11"/>
         <v>0.1089108910891089</v>
       </c>
@@ -29465,7 +29480,7 @@
       <c r="M84" s="4">
         <v>46272</v>
       </c>
-      <c r="N84" s="13">
+      <c r="N84" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>37</v>
       </c>
@@ -29489,7 +29504,7 @@
       <c r="B85" s="4">
         <v>46272</v>
       </c>
-      <c r="C85" s="13">
+      <c r="C85" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>37</v>
       </c>
@@ -29512,7 +29527,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>2.9702970297029702E-2</v>
       </c>
-      <c r="J85" s="13">
+      <c r="J85" s="1">
         <f t="shared" si="11"/>
         <v>0.97029702970297027</v>
       </c>
@@ -29520,13 +29535,34 @@
         <f>Tabla158[[#This Row],[FTQ]]</f>
         <v>0.97029702970297027</v>
       </c>
-      <c r="M85" s="4"/>
+      <c r="M85" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N85" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O85" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P85" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q85" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R85" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S85" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B86" s="4">
         <v>46272</v>
       </c>
-      <c r="C86" s="13">
+      <c r="C86" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>37</v>
       </c>
@@ -29549,7 +29585,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.69</v>
       </c>
-      <c r="J86" s="13">
+      <c r="J86" s="1">
         <f t="shared" si="11"/>
         <v>0.31000000000000005</v>
       </c>
@@ -29557,13 +29593,34 @@
         <f>Tabla158[[#This Row],[FTQ]]</f>
         <v>0.31000000000000005</v>
       </c>
-      <c r="M86" s="4"/>
+      <c r="M86" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N86" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P86" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q86" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R86" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="S86" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B87" s="4">
         <v>46272</v>
       </c>
-      <c r="C87" s="13">
+      <c r="C87" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>37</v>
       </c>
@@ -29586,7 +29643,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.16279069767441862</v>
       </c>
-      <c r="J87" s="13">
+      <c r="J87" s="1">
         <f t="shared" si="11"/>
         <v>0.83720930232558133</v>
       </c>
@@ -29594,13 +29651,34 @@
         <f>Tabla158[[#This Row],[FTQ]]</f>
         <v>0.83720930232558133</v>
       </c>
-      <c r="M87" s="4"/>
+      <c r="M87" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N87" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P87" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q87" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R87" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="S87" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
         <v>46272</v>
       </c>
-      <c r="C88" s="13">
+      <c r="C88" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>37</v>
       </c>
@@ -29623,7 +29701,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.20481927710843373</v>
       </c>
-      <c r="J88" s="13">
+      <c r="J88" s="1">
         <f>ABS(G$3-I88)</f>
         <v>0.79518072289156627</v>
       </c>
@@ -29631,13 +29709,34 @@
         <f>Tabla158[[#This Row],[FTQ]]</f>
         <v>0.79518072289156627</v>
       </c>
-      <c r="M88" s="4"/>
+      <c r="M88" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N88" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O88" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P88" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q88" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R88" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S88" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
         <v>46272</v>
       </c>
-      <c r="C89" s="13">
+      <c r="C89" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>37</v>
       </c>
@@ -29660,7 +29759,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.15555555555555556</v>
       </c>
-      <c r="J89" s="13">
+      <c r="J89" s="1">
         <f t="shared" si="11"/>
         <v>0.84444444444444444</v>
       </c>
@@ -29668,13 +29767,34 @@
         <f>Tabla158[[#This Row],[FTQ]]</f>
         <v>0.84444444444444444</v>
       </c>
-      <c r="M89" s="4"/>
+      <c r="M89" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N89" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P89" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q89" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R89" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S89" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
         <v>46272</v>
       </c>
-      <c r="C90" s="13">
+      <c r="C90" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>37</v>
       </c>
@@ -29697,7 +29817,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.21212121212121213</v>
       </c>
-      <c r="J90" s="13">
+      <c r="J90" s="1">
         <f>ABS(G$3-I90)</f>
         <v>0.78787878787878785</v>
       </c>
@@ -29705,62 +29825,430 @@
         <f>Tabla158[[#This Row],[FTQ]]</f>
         <v>0.78787878787878785</v>
       </c>
-      <c r="M90" s="4"/>
+      <c r="M90" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N90" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P90" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q90" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R90" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="S90" s="1">
+        <v>4</v>
+      </c>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B91" s="4"/>
-      <c r="I91" s="3"/>
-      <c r="J91" s="1"/>
-      <c r="K91" s="5"/>
-      <c r="M91" s="4"/>
+      <c r="B91" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C91" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E91" s="1">
+        <v>100</v>
+      </c>
+      <c r="F91" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G91" s="1">
+        <v>122</v>
+      </c>
+      <c r="H91" s="1">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>4.0983606557377046E-2</v>
+      </c>
+      <c r="J91" s="14">
+        <f t="shared" ref="J91:J97" si="12">ABS(G$3-I91)</f>
+        <v>0.95901639344262291</v>
+      </c>
+      <c r="K91" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.95901639344262291</v>
+      </c>
+      <c r="M91" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N91" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O91" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P91" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q91" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R91" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="S91" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B92" s="4"/>
-      <c r="I92" s="3"/>
-      <c r="J92" s="1"/>
-      <c r="K92" s="5"/>
-      <c r="M92" s="4"/>
+      <c r="B92" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C92" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E92" s="1">
+        <v>200</v>
+      </c>
+      <c r="F92" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G92" s="1">
+        <v>120</v>
+      </c>
+      <c r="H92" s="1">
+        <v>7</v>
+      </c>
+      <c r="I92" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>5.8333333333333334E-2</v>
+      </c>
+      <c r="J92" s="14">
+        <f t="shared" si="12"/>
+        <v>0.94166666666666665</v>
+      </c>
+      <c r="K92" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.94166666666666665</v>
+      </c>
+      <c r="M92" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N92" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P92" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q92" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R92" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="S92" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B93" s="4"/>
-      <c r="I93" s="3"/>
-      <c r="J93" s="1"/>
-      <c r="K93" s="5"/>
-      <c r="M93" s="4"/>
+      <c r="B93" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C93" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E93" s="1">
+        <v>300</v>
+      </c>
+      <c r="F93" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G93" s="1">
+        <v>100</v>
+      </c>
+      <c r="H93" s="1">
+        <v>3</v>
+      </c>
+      <c r="I93" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.03</v>
+      </c>
+      <c r="J93" s="14">
+        <f t="shared" si="12"/>
+        <v>0.97</v>
+      </c>
+      <c r="K93" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.97</v>
+      </c>
+      <c r="M93" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N93" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O93" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P93" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q93" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R93" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S93" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B94" s="4"/>
-      <c r="I94" s="3"/>
-      <c r="J94" s="1"/>
-      <c r="K94" s="5"/>
-      <c r="M94" s="4"/>
+      <c r="B94" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C94" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E94" s="1">
+        <v>400</v>
+      </c>
+      <c r="F94" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G94" s="1">
+        <v>119</v>
+      </c>
+      <c r="H94" s="1">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>3.3613445378151259E-2</v>
+      </c>
+      <c r="J94" s="14">
+        <f t="shared" si="12"/>
+        <v>0.96638655462184875</v>
+      </c>
+      <c r="K94" s="12">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.96638655462184875</v>
+      </c>
+      <c r="M94" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N94" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P94" s="1">
+        <v>800</v>
+      </c>
+      <c r="Q94" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R94" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="S94" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B95" s="4"/>
-      <c r="I95" s="3"/>
-      <c r="J95" s="1"/>
-      <c r="K95" s="5"/>
-      <c r="M95" s="4"/>
+      <c r="B95" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C95" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E95" s="1">
+        <v>500</v>
+      </c>
+      <c r="F95" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G95" s="1">
+        <v>124</v>
+      </c>
+      <c r="H95" s="1">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J95" s="14">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="K95" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M95" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N95" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P95" s="1">
+        <v>800</v>
+      </c>
+      <c r="Q95" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R95" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="S95" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B96" s="4"/>
-      <c r="I96" s="3"/>
-      <c r="J96" s="1"/>
-      <c r="K96" s="5"/>
+      <c r="B96" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C96" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E96" s="1">
+        <v>600</v>
+      </c>
+      <c r="F96" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G96" s="1">
+        <v>119</v>
+      </c>
+      <c r="H96" s="1">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>4.2016806722689079E-2</v>
+      </c>
+      <c r="J96" s="14">
+        <f t="shared" si="12"/>
+        <v>0.95798319327731096</v>
+      </c>
+      <c r="K96" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.95798319327731096</v>
+      </c>
       <c r="M96" s="4"/>
+      <c r="N96" s="14"/>
+      <c r="Q96" s="9"/>
     </row>
     <row r="97" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B97" s="4"/>
-      <c r="I97" s="3"/>
-      <c r="J97" s="1"/>
-      <c r="K97" s="5"/>
+      <c r="B97" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C97" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E97" s="1">
+        <v>700</v>
+      </c>
+      <c r="F97" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G97" s="1">
+        <v>118</v>
+      </c>
+      <c r="H97" s="1">
+        <v>2</v>
+      </c>
+      <c r="I97" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="J97" s="14">
+        <f t="shared" si="12"/>
+        <v>0.98305084745762716</v>
+      </c>
+      <c r="K97" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.98305084745762716</v>
+      </c>
       <c r="M97" s="4"/>
     </row>
     <row r="98" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B98" s="4"/>
-      <c r="I98" s="3"/>
-      <c r="J98" s="1"/>
-      <c r="K98" s="5"/>
+      <c r="B98" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C98" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E98" s="1">
+        <v>800</v>
+      </c>
+      <c r="F98" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G98" s="1">
+        <v>112</v>
+      </c>
+      <c r="H98" s="1">
+        <v>4</v>
+      </c>
+      <c r="I98" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="J98" s="14">
+        <f>ABS(G$3-I98)</f>
+        <v>0.9642857142857143</v>
+      </c>
+      <c r="K98" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.9642857142857143</v>
+      </c>
       <c r="M98" s="4"/>
     </row>
     <row r="99" spans="2:13" x14ac:dyDescent="0.3">

--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\5_MB MMA\09_Information\10_FTQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37415832-24D7-4459-BC2D-E251FB0DFDD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA26118-178C-4B38-9FCF-F7963EE9180A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$110</definedName>
     <definedName name="DATA_01">[1]Data_Lineal!$H$4:$Y$30</definedName>
     <definedName name="DB_01">#REF!</definedName>
     <definedName name="DB_CAP01">'[2]CAPACIDAD (1)'!$X$9:$AM$29</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="85">
   <si>
     <t>*</t>
   </si>
@@ -24429,7 +24429,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K98" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K110" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CDAA4D20-2955-41E2-BD7E-9330E166FFF4}" name="Fecha" dataDxfId="18"/>
     <tableColumn id="9" xr3:uid="{F70BB124-92DE-4024-874C-EE3BA966CDE6}" name="Semana" dataDxfId="17">
@@ -24455,7 +24455,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S95" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S111" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="07/09/2026" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="37" dataDxfId="5">
@@ -29538,7 +29538,7 @@
       <c r="M85" s="4">
         <v>46282</v>
       </c>
-      <c r="N85" s="14">
+      <c r="N85" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>38</v>
       </c>
@@ -29596,7 +29596,7 @@
       <c r="M86" s="4">
         <v>46282</v>
       </c>
-      <c r="N86" s="14">
+      <c r="N86" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>38</v>
       </c>
@@ -29654,7 +29654,7 @@
       <c r="M87" s="4">
         <v>46282</v>
       </c>
-      <c r="N87" s="14">
+      <c r="N87" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>38</v>
       </c>
@@ -29712,7 +29712,7 @@
       <c r="M88" s="4">
         <v>46282</v>
       </c>
-      <c r="N88" s="14">
+      <c r="N88" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>38</v>
       </c>
@@ -29770,7 +29770,7 @@
       <c r="M89" s="4">
         <v>46282</v>
       </c>
-      <c r="N89" s="14">
+      <c r="N89" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>38</v>
       </c>
@@ -29828,7 +29828,7 @@
       <c r="M90" s="4">
         <v>46282</v>
       </c>
-      <c r="N90" s="14">
+      <c r="N90" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>38</v>
       </c>
@@ -29852,7 +29852,7 @@
       <c r="B91" s="4">
         <v>46282</v>
       </c>
-      <c r="C91" s="14">
+      <c r="C91" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>38</v>
       </c>
@@ -29875,7 +29875,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>4.0983606557377046E-2</v>
       </c>
-      <c r="J91" s="14">
+      <c r="J91" s="1">
         <f t="shared" ref="J91:J97" si="12">ABS(G$3-I91)</f>
         <v>0.95901639344262291</v>
       </c>
@@ -29886,7 +29886,7 @@
       <c r="M91" s="4">
         <v>46282</v>
       </c>
-      <c r="N91" s="14">
+      <c r="N91" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>38</v>
       </c>
@@ -29910,7 +29910,7 @@
       <c r="B92" s="4">
         <v>46282</v>
       </c>
-      <c r="C92" s="14">
+      <c r="C92" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>38</v>
       </c>
@@ -29933,7 +29933,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>5.8333333333333334E-2</v>
       </c>
-      <c r="J92" s="14">
+      <c r="J92" s="1">
         <f t="shared" si="12"/>
         <v>0.94166666666666665</v>
       </c>
@@ -29944,7 +29944,7 @@
       <c r="M92" s="4">
         <v>46282</v>
       </c>
-      <c r="N92" s="14">
+      <c r="N92" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>38</v>
       </c>
@@ -29968,7 +29968,7 @@
       <c r="B93" s="4">
         <v>46282</v>
       </c>
-      <c r="C93" s="14">
+      <c r="C93" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>38</v>
       </c>
@@ -29991,7 +29991,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.03</v>
       </c>
-      <c r="J93" s="14">
+      <c r="J93" s="1">
         <f t="shared" si="12"/>
         <v>0.97</v>
       </c>
@@ -30002,7 +30002,7 @@
       <c r="M93" s="4">
         <v>46282</v>
       </c>
-      <c r="N93" s="14">
+      <c r="N93" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>38</v>
       </c>
@@ -30026,7 +30026,7 @@
       <c r="B94" s="4">
         <v>46282</v>
       </c>
-      <c r="C94" s="14">
+      <c r="C94" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>38</v>
       </c>
@@ -30049,7 +30049,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>3.3613445378151259E-2</v>
       </c>
-      <c r="J94" s="14">
+      <c r="J94" s="1">
         <f t="shared" si="12"/>
         <v>0.96638655462184875</v>
       </c>
@@ -30060,7 +30060,7 @@
       <c r="M94" s="4">
         <v>46282</v>
       </c>
-      <c r="N94" s="14">
+      <c r="N94" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>38</v>
       </c>
@@ -30084,7 +30084,7 @@
       <c r="B95" s="4">
         <v>46282</v>
       </c>
-      <c r="C95" s="14">
+      <c r="C95" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>38</v>
       </c>
@@ -30107,7 +30107,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J95" s="14">
+      <c r="J95" s="1">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
@@ -30118,7 +30118,7 @@
       <c r="M95" s="4">
         <v>46282</v>
       </c>
-      <c r="N95" s="14">
+      <c r="N95" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>38</v>
       </c>
@@ -30142,7 +30142,7 @@
       <c r="B96" s="4">
         <v>46282</v>
       </c>
-      <c r="C96" s="14">
+      <c r="C96" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>38</v>
       </c>
@@ -30165,7 +30165,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>4.2016806722689079E-2</v>
       </c>
-      <c r="J96" s="14">
+      <c r="J96" s="1">
         <f t="shared" si="12"/>
         <v>0.95798319327731096</v>
       </c>
@@ -30173,15 +30173,20 @@
         <f>Tabla158[[#This Row],[FTQ]]</f>
         <v>0.95798319327731096</v>
       </c>
-      <c r="M96" s="4"/>
-      <c r="N96" s="14"/>
+      <c r="M96" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N96" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
       <c r="Q96" s="9"/>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
         <v>46282</v>
       </c>
-      <c r="C97" s="14">
+      <c r="C97" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>38</v>
       </c>
@@ -30204,7 +30209,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>1.6949152542372881E-2</v>
       </c>
-      <c r="J97" s="14">
+      <c r="J97" s="1">
         <f t="shared" si="12"/>
         <v>0.98305084745762716</v>
       </c>
@@ -30212,13 +30217,20 @@
         <f>Tabla158[[#This Row],[FTQ]]</f>
         <v>0.98305084745762716</v>
       </c>
-      <c r="M97" s="4"/>
-    </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M97" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N97" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="Q97" s="9"/>
+    </row>
+    <row r="98" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
         <v>46282</v>
       </c>
-      <c r="C98" s="14">
+      <c r="C98" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>38</v>
       </c>
@@ -30241,7 +30253,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>3.5714285714285712E-2</v>
       </c>
-      <c r="J98" s="14">
+      <c r="J98" s="1">
         <f>ABS(G$3-I98)</f>
         <v>0.9642857142857143</v>
       </c>
@@ -30249,117 +30261,583 @@
         <f>Tabla158[[#This Row],[FTQ]]</f>
         <v>0.9642857142857143</v>
       </c>
-      <c r="M98" s="4"/>
-    </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B99" s="4"/>
-      <c r="I99" s="3"/>
-      <c r="J99" s="1"/>
-      <c r="K99" s="5"/>
-      <c r="M99" s="4"/>
-    </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B100" s="4"/>
-      <c r="I100" s="3"/>
-      <c r="J100" s="1"/>
-      <c r="K100" s="5"/>
-      <c r="M100" s="4"/>
-    </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B101" s="4"/>
-      <c r="I101" s="3"/>
-      <c r="J101" s="1"/>
-      <c r="K101" s="5"/>
-      <c r="M101" s="4"/>
-    </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B102" s="4"/>
-      <c r="I102" s="3"/>
-      <c r="J102" s="1"/>
-      <c r="K102" s="5"/>
-      <c r="M102" s="4"/>
-    </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B103" s="4"/>
-      <c r="I103" s="3"/>
-      <c r="J103" s="1"/>
-      <c r="K103" s="5"/>
-      <c r="M103" s="4"/>
-    </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B104" s="4"/>
-      <c r="I104" s="3"/>
-      <c r="J104" s="1"/>
-      <c r="K104" s="5"/>
-      <c r="M104" s="4"/>
-    </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B105" s="4"/>
-      <c r="I105" s="3"/>
-      <c r="J105" s="1"/>
-      <c r="K105" s="5"/>
-      <c r="M105" s="4"/>
-    </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B106" s="4"/>
-      <c r="I106" s="3"/>
-      <c r="J106" s="1"/>
-      <c r="K106" s="5"/>
-      <c r="M106" s="4"/>
-    </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B107" s="4"/>
-      <c r="I107" s="3"/>
-      <c r="J107" s="1"/>
-      <c r="K107" s="5"/>
-      <c r="M107" s="4"/>
-    </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B108" s="4"/>
-      <c r="I108" s="3"/>
-      <c r="J108" s="1"/>
-      <c r="K108" s="5"/>
-      <c r="M108" s="4"/>
-    </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B109" s="4"/>
-      <c r="I109" s="3"/>
-      <c r="J109" s="1"/>
-      <c r="K109" s="5"/>
-      <c r="M109" s="4"/>
-    </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B110" s="4"/>
-      <c r="I110" s="3"/>
-      <c r="J110" s="1"/>
-      <c r="K110" s="5"/>
-      <c r="M110" s="4"/>
-    </row>
-    <row r="111" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M98" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N98" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="Q98" s="9"/>
+    </row>
+    <row r="99" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B99" s="4">
+        <v>46289</v>
+      </c>
+      <c r="C99" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>39</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E99" s="1">
+        <v>100</v>
+      </c>
+      <c r="F99" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G99" s="1">
+        <v>94</v>
+      </c>
+      <c r="H99" s="1">
+        <v>6</v>
+      </c>
+      <c r="I99" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>6.3829787234042548E-2</v>
+      </c>
+      <c r="J99" s="14">
+        <f t="shared" ref="J99:J114" si="13">ABS(G$3-I99)</f>
+        <v>0.93617021276595747</v>
+      </c>
+      <c r="K99" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.93617021276595747</v>
+      </c>
+      <c r="M99" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N99" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="Q99" s="9"/>
+    </row>
+    <row r="100" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B100" s="4">
+        <v>46289</v>
+      </c>
+      <c r="C100" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>39</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E100" s="1">
+        <v>200</v>
+      </c>
+      <c r="F100" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G100" s="1">
+        <v>99</v>
+      </c>
+      <c r="H100" s="1">
+        <v>1</v>
+      </c>
+      <c r="I100" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>1.0101010101010102E-2</v>
+      </c>
+      <c r="J100" s="14">
+        <f t="shared" si="13"/>
+        <v>0.98989898989898994</v>
+      </c>
+      <c r="K100" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.98989898989898994</v>
+      </c>
+      <c r="M100" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N100" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="Q100" s="9"/>
+    </row>
+    <row r="101" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B101" s="4">
+        <v>46289</v>
+      </c>
+      <c r="C101" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>39</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E101" s="1">
+        <v>300</v>
+      </c>
+      <c r="F101" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G101" s="1">
+        <v>95</v>
+      </c>
+      <c r="H101" s="1">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="J101" s="14">
+        <f t="shared" si="13"/>
+        <v>0.94736842105263164</v>
+      </c>
+      <c r="K101" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.94736842105263164</v>
+      </c>
+      <c r="M101" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N101" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="Q101" s="9"/>
+    </row>
+    <row r="102" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B102" s="4">
+        <v>46289</v>
+      </c>
+      <c r="C102" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>39</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E102" s="1">
+        <v>400</v>
+      </c>
+      <c r="F102" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G102" s="1">
+        <v>91</v>
+      </c>
+      <c r="H102" s="1">
+        <v>9</v>
+      </c>
+      <c r="I102" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>9.8901098901098897E-2</v>
+      </c>
+      <c r="J102" s="14">
+        <f t="shared" si="13"/>
+        <v>0.90109890109890112</v>
+      </c>
+      <c r="K102" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.90109890109890112</v>
+      </c>
+      <c r="M102" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N102" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="Q102" s="9"/>
+    </row>
+    <row r="103" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B103" s="4">
+        <v>46289</v>
+      </c>
+      <c r="C103" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>39</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E103" s="1">
+        <v>500</v>
+      </c>
+      <c r="F103" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G103" s="1">
+        <v>95</v>
+      </c>
+      <c r="H103" s="1">
+        <v>0</v>
+      </c>
+      <c r="I103" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J103" s="14">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="K103" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M103" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N103" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="Q103" s="9"/>
+    </row>
+    <row r="104" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B104" s="4">
+        <v>46289</v>
+      </c>
+      <c r="C104" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>39</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E104" s="1">
+        <v>600</v>
+      </c>
+      <c r="F104" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G104" s="1">
+        <v>93</v>
+      </c>
+      <c r="H104" s="1">
+        <v>2</v>
+      </c>
+      <c r="I104" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>2.1505376344086023E-2</v>
+      </c>
+      <c r="J104" s="14">
+        <f t="shared" si="13"/>
+        <v>0.978494623655914</v>
+      </c>
+      <c r="K104" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.978494623655914</v>
+      </c>
+      <c r="M104" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N104" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="Q104" s="9"/>
+    </row>
+    <row r="105" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B105" s="4">
+        <v>46289</v>
+      </c>
+      <c r="C105" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>39</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E105" s="1">
+        <v>700</v>
+      </c>
+      <c r="F105" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G105" s="1">
+        <v>69</v>
+      </c>
+      <c r="H105" s="1">
+        <v>30</v>
+      </c>
+      <c r="I105" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.43478260869565216</v>
+      </c>
+      <c r="J105" s="14">
+        <f t="shared" si="13"/>
+        <v>0.56521739130434789</v>
+      </c>
+      <c r="K105" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.56521739130434789</v>
+      </c>
+      <c r="M105" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N105" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="Q105" s="9"/>
+    </row>
+    <row r="106" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B106" s="4">
+        <v>46289</v>
+      </c>
+      <c r="C106" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>39</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E106" s="1">
+        <v>800</v>
+      </c>
+      <c r="F106" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G106" s="1">
+        <v>96</v>
+      </c>
+      <c r="H106" s="1">
+        <v>3</v>
+      </c>
+      <c r="I106" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="J106" s="14">
+        <f t="shared" si="13"/>
+        <v>0.96875</v>
+      </c>
+      <c r="K106" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.96875</v>
+      </c>
+      <c r="M106" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N106" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="Q106" s="9"/>
+    </row>
+    <row r="107" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B107" s="4">
+        <v>46289</v>
+      </c>
+      <c r="C107" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>39</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E107" s="1">
+        <v>900</v>
+      </c>
+      <c r="F107" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G107" s="1">
+        <v>80</v>
+      </c>
+      <c r="H107" s="1">
+        <v>20</v>
+      </c>
+      <c r="I107" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.25</v>
+      </c>
+      <c r="J107" s="14">
+        <f t="shared" si="13"/>
+        <v>0.75</v>
+      </c>
+      <c r="K107" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.75</v>
+      </c>
+      <c r="M107" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N107" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="Q107" s="9"/>
+    </row>
+    <row r="108" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B108" s="4">
+        <v>46289</v>
+      </c>
+      <c r="C108" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>39</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E108" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F108" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G108" s="1">
+        <v>77</v>
+      </c>
+      <c r="H108" s="1">
+        <v>23</v>
+      </c>
+      <c r="I108" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.29870129870129869</v>
+      </c>
+      <c r="J108" s="14">
+        <f t="shared" si="13"/>
+        <v>0.70129870129870131</v>
+      </c>
+      <c r="K108" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.70129870129870131</v>
+      </c>
+      <c r="M108" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N108" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="Q108" s="9"/>
+    </row>
+    <row r="109" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B109" s="4">
+        <v>46289</v>
+      </c>
+      <c r="C109" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>39</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E109" s="1">
+        <v>1100</v>
+      </c>
+      <c r="F109" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G109" s="1">
+        <v>70</v>
+      </c>
+      <c r="H109" s="1">
+        <v>4</v>
+      </c>
+      <c r="I109" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="J109" s="14">
+        <f t="shared" si="13"/>
+        <v>0.94285714285714284</v>
+      </c>
+      <c r="K109" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.94285714285714284</v>
+      </c>
+      <c r="M109" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N109" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="Q109" s="9"/>
+    </row>
+    <row r="110" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B110" s="4">
+        <v>46289</v>
+      </c>
+      <c r="C110" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>39</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E110" s="1">
+        <v>1200</v>
+      </c>
+      <c r="F110" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G110" s="1">
+        <v>39</v>
+      </c>
+      <c r="H110" s="1">
+        <v>12</v>
+      </c>
+      <c r="I110" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="J110" s="14">
+        <f t="shared" si="13"/>
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="K110" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="M110" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N110" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="Q110" s="9"/>
+    </row>
+    <row r="111" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B111" s="4"/>
+      <c r="C111" s="14"/>
+      <c r="F111" s="9"/>
       <c r="I111" s="3"/>
-      <c r="J111" s="1"/>
+      <c r="J111" s="14"/>
       <c r="K111" s="5"/>
-      <c r="M111" s="4"/>
-    </row>
-    <row r="112" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M111" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N111" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="Q111" s="9"/>
+    </row>
+    <row r="112" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B112" s="4"/>
+      <c r="C112" s="14"/>
+      <c r="F112" s="9"/>
       <c r="I112" s="3"/>
-      <c r="J112" s="1"/>
+      <c r="J112" s="14"/>
       <c r="K112" s="5"/>
       <c r="M112" s="4"/>
     </row>
     <row r="113" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B113" s="4"/>
+      <c r="C113" s="14"/>
+      <c r="F113" s="9"/>
       <c r="I113" s="3"/>
-      <c r="J113" s="1"/>
+      <c r="J113" s="14"/>
       <c r="K113" s="5"/>
       <c r="M113" s="4"/>
     </row>
     <row r="114" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B114" s="4"/>
+      <c r="C114" s="14"/>
+      <c r="F114" s="9"/>
       <c r="I114" s="3"/>
-      <c r="J114" s="1"/>
+      <c r="J114" s="14"/>
       <c r="K114" s="5"/>
       <c r="M114" s="4"/>
     </row>

--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\5_MB MMA\09_Information\10_FTQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA26118-178C-4B38-9FCF-F7963EE9180A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74F80C2-175A-49A3-8903-3A7F3DD90E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE DE DATOS" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$135</definedName>
     <definedName name="DATA_01">[1]Data_Lineal!$H$4:$Y$30</definedName>
     <definedName name="DB_01">#REF!</definedName>
     <definedName name="DB_CAP01">'[2]CAPACIDAD (1)'!$X$9:$AM$29</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="115">
   <si>
     <t>*</t>
   </si>
@@ -166,9 +166,6 @@
   </si>
   <si>
     <t>Sensor no detecta mesa giratoria Op.400</t>
-  </si>
-  <si>
-    <t>Falla en inspección visual de Ruteo de Arnes Op.700</t>
   </si>
   <si>
     <t>Falla en alimentador de Tornillos Op.800</t>
@@ -318,7 +315,100 @@
     <t>Mal ensamble de elemento de compensación en rodamiento Op.400</t>
   </si>
   <si>
-    <t>No ensambla tornillo</t>
+    <t>No detecta el anillo metálico, falla visual de cámara</t>
+  </si>
+  <si>
+    <t>Error de comunicación Twin Safe Op.100</t>
+  </si>
+  <si>
+    <t>Falla en clampeo del Housing SAS Op.200</t>
+  </si>
+  <si>
+    <t>Fractura de Rodamiento Op.400</t>
+  </si>
+  <si>
+    <t>Falla de Inspección visual  del SCAS Op.700</t>
+  </si>
+  <si>
+    <t>Cable Dummy con Rebaba Op.150</t>
+  </si>
+  <si>
+    <t>Falla en altura en cable Dummy Op.200</t>
+  </si>
+  <si>
+    <t>Falla en Sensor Z3a Op.200</t>
+  </si>
+  <si>
+    <t>Latch no Bloquea giro en Pieza Op. EOL</t>
+  </si>
+  <si>
+    <t>Falla 6000.001 retrabajo piezas OK Op.EOL</t>
+  </si>
+  <si>
+    <t>Falla 2330.031 Op. EOL</t>
+  </si>
+  <si>
+    <t>safelaunch</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual en Lectura de QR de PCB Op.200</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual en Lectura de QR de PCB Op.300</t>
+  </si>
+  <si>
+    <t>Falla en inspección visual de Ruteo de Arnes en Palancas Op.700</t>
+  </si>
+  <si>
+    <t>Falla 0005.005 - Mal acomodo de Etiqueta Op.Calibrador de Palancas</t>
+  </si>
+  <si>
+    <t>Falla CALL_WAIT_MOVE_ROBOT_ONE_STEP  Op.Calibrador de Palancas</t>
+  </si>
+  <si>
+    <t>Falla 2045 CALL_CHECK_LEVER Op.Calibrador de Palancas</t>
+  </si>
+  <si>
+    <t>Falla 2000 GET_CUSTOMER_NO Op.Calibrador de Palancas</t>
+  </si>
+  <si>
+    <t>Falla 2005 KOSTIA_LOGIN Op.Calibrador de Palancas</t>
+  </si>
+  <si>
+    <t>Falla 2500  Fluctuación de señal en Palanca SBW Op.Calibrador de Palancas</t>
+  </si>
+  <si>
+    <t>Falla 2400 Mesetas en Palanca TS Op.Calibrador de Palancas</t>
+  </si>
+  <si>
+    <t>Falla 2110 CALL_EVAULATE_WFK_TEST Op.Pruebas de Ruido</t>
+  </si>
+  <si>
+    <t>Falla 6100 CALL_WFK TEST Op.Pruebas de Ruido</t>
+  </si>
+  <si>
+    <t>Call evaluate TIHB RIGHT UNLOCKING Op.Pruebas de Ruido</t>
+  </si>
+  <si>
+    <t>Falla 3006 de comando Sleep Mode Op.Calibrador de iluminación</t>
+  </si>
+  <si>
+    <t>Falla 3002 Falla de medición eléctrica AB1 Op.Calibrador de iluminación</t>
+  </si>
+  <si>
+    <t>Falla 3000 Check LK Number Op.Calibrador de iluminación</t>
+  </si>
+  <si>
+    <t>Falla 8100 Falla configuración SAS / MLX Op.Calibrador SAS2</t>
+  </si>
+  <si>
+    <t>Falla 4015 CALL_CONNECT_KOSTIA Op.Calibrador SAS2</t>
+  </si>
+  <si>
+    <t>Falla 7510 - Lectura de Botón Parking Op. EOL</t>
+  </si>
+  <si>
+    <t>Falla 7000 GET_ARTICLE_NR_SCM Op. EOL</t>
   </si>
 </sst>
 </file>
@@ -447,7 +537,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="21">
     <dxf>
@@ -24429,7 +24519,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K110" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K135" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CDAA4D20-2955-41E2-BD7E-9330E166FFF4}" name="Fecha" dataDxfId="18"/>
     <tableColumn id="9" xr3:uid="{F70BB124-92DE-4024-874C-EE3BA966CDE6}" name="Semana" dataDxfId="17">
@@ -24455,7 +24545,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S111" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S141" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="07/09/2026" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="37" dataDxfId="5">
@@ -24736,7 +24826,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A1B645-8848-474A-88BA-FA9209B01B4F}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:V824"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
     <col min="2" max="2" width="13.21875" style="1" customWidth="1"/>
@@ -24839,19 +24929,19 @@
         <v>8</v>
       </c>
       <c r="M4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>30</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>2</v>
@@ -25782,7 +25872,7 @@
         <v>12289497</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S20" s="1">
         <v>6</v>
@@ -25840,7 +25930,7 @@
         <v>12289497</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S21" s="1">
         <v>12</v>
@@ -26072,7 +26162,7 @@
         <v>12289497</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="S25" s="1">
         <v>45</v>
@@ -26130,7 +26220,7 @@
         <v>12289497</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S26" s="1">
         <v>3</v>
@@ -26246,7 +26336,7 @@
         <v>12289475</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S28" s="1">
         <v>5</v>
@@ -26304,7 +26394,7 @@
         <v>12289475</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S29" s="1">
         <v>3</v>
@@ -26420,7 +26510,7 @@
         <v>12289475</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S31" s="1">
         <v>3</v>
@@ -26478,7 +26568,7 @@
         <v>12289475</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S32" s="1">
         <v>2</v>
@@ -26536,7 +26626,7 @@
         <v>12289475</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S33" s="1">
         <v>2</v>
@@ -26594,7 +26684,7 @@
         <v>12289475</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S34" s="1">
         <v>2</v>
@@ -26652,7 +26742,7 @@
         <v>12289497</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S35" s="1">
         <v>6</v>
@@ -26710,7 +26800,7 @@
         <v>12289497</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S36" s="1">
         <v>3</v>
@@ -26826,7 +26916,7 @@
         <v>12289497</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S38" s="1">
         <v>5</v>
@@ -26942,7 +27032,7 @@
         <v>12289497</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S40" s="1">
         <v>15</v>
@@ -27000,7 +27090,7 @@
         <v>12289497</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S41" s="1">
         <v>5</v>
@@ -27058,7 +27148,7 @@
         <v>10532587</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S42" s="1">
         <v>13</v>
@@ -27116,7 +27206,7 @@
         <v>10532587</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S43" s="1">
         <v>18</v>
@@ -27232,7 +27322,7 @@
         <v>10532587</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S45" s="1">
         <v>15</v>
@@ -27290,7 +27380,7 @@
         <v>10532587</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S46" s="1">
         <v>1</v>
@@ -27348,7 +27438,7 @@
         <v>10532587</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S47" s="1">
         <v>6</v>
@@ -27406,7 +27496,7 @@
         <v>10532587</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S48" s="1">
         <v>27</v>
@@ -27522,7 +27612,7 @@
         <v>10532587</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S50" s="1">
         <v>2</v>
@@ -27638,7 +27728,7 @@
         <v>10532587</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S52" s="1">
         <v>9</v>
@@ -27696,7 +27786,7 @@
         <v>10532587</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S53" s="1">
         <v>5</v>
@@ -27754,7 +27844,7 @@
         <v>10532587</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S54" s="1">
         <v>18</v>
@@ -27812,7 +27902,7 @@
         <v>10532587</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S55" s="1">
         <v>6</v>
@@ -27928,7 +28018,7 @@
         <v>10532587</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S57" s="1">
         <v>2</v>
@@ -28044,7 +28134,7 @@
         <v>10532587</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S59" s="1">
         <v>10</v>
@@ -28102,7 +28192,7 @@
         <v>10532587</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S60" s="1">
         <v>2</v>
@@ -28160,7 +28250,7 @@
         <v>10532587</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S61" s="1">
         <v>2</v>
@@ -28218,7 +28308,7 @@
         <v>10532587</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S62" s="1">
         <v>1</v>
@@ -28276,7 +28366,7 @@
         <v>10532587</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S63" s="1">
         <v>1</v>
@@ -28450,7 +28540,7 @@
         <v>10532587</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S66" s="1">
         <v>10</v>
@@ -28508,7 +28598,7 @@
         <v>12289507</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S67" s="1">
         <v>6</v>
@@ -28566,7 +28656,7 @@
         <v>12289507</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S68" s="1">
         <v>5</v>
@@ -28624,7 +28714,7 @@
         <v>12289507</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S69" s="1">
         <v>1</v>
@@ -28676,13 +28766,13 @@
         <v>30</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q70" s="9">
         <v>12289507</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="S70" s="1">
         <v>9</v>
@@ -28740,7 +28830,7 @@
         <v>12289507</v>
       </c>
       <c r="R71" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S71" s="1">
         <v>15</v>
@@ -28798,7 +28888,7 @@
         <v>12289507</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S72" s="1">
         <v>3</v>
@@ -28856,7 +28946,7 @@
         <v>12289507</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S73" s="1">
         <v>2</v>
@@ -28914,7 +29004,7 @@
         <v>12289507</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S74" s="1">
         <v>10</v>
@@ -28932,7 +29022,7 @@
         <v>30</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F75" s="9">
         <v>12289507</v>
@@ -28972,7 +29062,7 @@
         <v>12289507</v>
       </c>
       <c r="R75" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S75" s="1">
         <v>50</v>
@@ -28990,7 +29080,7 @@
         <v>30</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F76" s="9">
         <v>12289507</v>
@@ -29030,7 +29120,7 @@
         <v>12289507</v>
       </c>
       <c r="R76" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S76" s="1">
         <v>20</v>
@@ -29048,7 +29138,7 @@
         <v>30</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F77" s="9">
         <v>12289507</v>
@@ -29088,7 +29178,7 @@
         <v>12289507</v>
       </c>
       <c r="R77" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S77" s="1">
         <v>90</v>
@@ -29146,7 +29236,7 @@
         <v>12289507</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S78" s="1">
         <v>3</v>
@@ -29198,13 +29288,13 @@
         <v>30</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q79" s="9">
         <v>12289507</v>
       </c>
       <c r="R79" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="S79" s="1">
         <v>69</v>
@@ -29256,13 +29346,13 @@
         <v>30</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q80" s="9">
         <v>12289507</v>
       </c>
       <c r="R80" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S80" s="1">
         <v>10</v>
@@ -29314,13 +29404,13 @@
         <v>30</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q81" s="9">
         <v>12289507</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S81" s="1">
         <v>4</v>
@@ -29372,13 +29462,13 @@
         <v>30</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q82" s="9">
         <v>12289507</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S82" s="1">
         <v>17</v>
@@ -29430,13 +29520,13 @@
         <v>30</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q83" s="9">
         <v>12289507</v>
       </c>
       <c r="R83" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S83" s="1">
         <v>7</v>
@@ -29488,13 +29578,13 @@
         <v>30</v>
       </c>
       <c r="P84" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q84" s="9">
         <v>12289507</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S84" s="1">
         <v>7</v>
@@ -29552,7 +29642,7 @@
         <v>12289507</v>
       </c>
       <c r="R85" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S85" s="1">
         <v>2</v>
@@ -29570,7 +29660,7 @@
         <v>30</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F86" s="9">
         <v>12289507</v>
@@ -29610,7 +29700,7 @@
         <v>12289507</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S86" s="1">
         <v>3</v>
@@ -29628,7 +29718,7 @@
         <v>30</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F87" s="9">
         <v>12289507</v>
@@ -29668,7 +29758,7 @@
         <v>12289507</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S87" s="1">
         <v>3</v>
@@ -29686,7 +29776,7 @@
         <v>30</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F88" s="9">
         <v>12289507</v>
@@ -29744,7 +29834,7 @@
         <v>30</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F89" s="9">
         <v>12289507</v>
@@ -29784,7 +29874,7 @@
         <v>12289507</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S89" s="1">
         <v>3</v>
@@ -29802,7 +29892,7 @@
         <v>30</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F90" s="9">
         <v>12289507</v>
@@ -29842,7 +29932,7 @@
         <v>12289507</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S90" s="1">
         <v>4</v>
@@ -29900,7 +29990,7 @@
         <v>12289507</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S91" s="1">
         <v>3</v>
@@ -29958,7 +30048,7 @@
         <v>12289507</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S92" s="1">
         <v>2</v>
@@ -30016,7 +30106,7 @@
         <v>12289507</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="S93" s="1">
         <v>2</v>
@@ -30074,7 +30164,7 @@
         <v>12289507</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S94" s="1">
         <v>2</v>
@@ -30132,7 +30222,7 @@
         <v>12289507</v>
       </c>
       <c r="R95" s="1" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="S95" s="1">
         <v>2</v>
@@ -30176,13 +30266,27 @@
       <c r="M96" s="4">
         <v>46289</v>
       </c>
-      <c r="N96" s="14">
+      <c r="N96" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q96" s="9"/>
-    </row>
-    <row r="97" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O96" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P96" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q96" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R96" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="S96" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
         <v>46282</v>
       </c>
@@ -30220,13 +30324,27 @@
       <c r="M97" s="4">
         <v>46289</v>
       </c>
-      <c r="N97" s="14">
+      <c r="N97" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q97" s="9"/>
-    </row>
-    <row r="98" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O97" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P97" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q97" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R97" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="S97" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
         <v>46282</v>
       </c>
@@ -30264,17 +30382,31 @@
       <c r="M98" s="4">
         <v>46289</v>
       </c>
-      <c r="N98" s="14">
+      <c r="N98" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q98" s="9"/>
-    </row>
-    <row r="99" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O98" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P98" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q98" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R98" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="S98" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
         <v>46289</v>
       </c>
-      <c r="C99" s="14">
+      <c r="C99" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>39</v>
       </c>
@@ -30297,8 +30429,8 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>6.3829787234042548E-2</v>
       </c>
-      <c r="J99" s="14">
-        <f t="shared" ref="J99:J114" si="13">ABS(G$3-I99)</f>
+      <c r="J99" s="1">
+        <f t="shared" ref="J99:J110" si="13">ABS(G$3-I99)</f>
         <v>0.93617021276595747</v>
       </c>
       <c r="K99" s="5">
@@ -30308,17 +30440,31 @@
       <c r="M99" s="4">
         <v>46289</v>
       </c>
-      <c r="N99" s="14">
+      <c r="N99" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q99" s="9"/>
-    </row>
-    <row r="100" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O99" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P99" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q99" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R99" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="S99" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B100" s="4">
         <v>46289</v>
       </c>
-      <c r="C100" s="14">
+      <c r="C100" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>39</v>
       </c>
@@ -30341,7 +30487,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>1.0101010101010102E-2</v>
       </c>
-      <c r="J100" s="14">
+      <c r="J100" s="1">
         <f t="shared" si="13"/>
         <v>0.98989898989898994</v>
       </c>
@@ -30352,17 +30498,31 @@
       <c r="M100" s="4">
         <v>46289</v>
       </c>
-      <c r="N100" s="14">
+      <c r="N100" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q100" s="9"/>
-    </row>
-    <row r="101" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O100" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P100" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q100" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R100" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="S100" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B101" s="4">
         <v>46289</v>
       </c>
-      <c r="C101" s="14">
+      <c r="C101" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>39</v>
       </c>
@@ -30385,7 +30545,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>5.2631578947368418E-2</v>
       </c>
-      <c r="J101" s="14">
+      <c r="J101" s="1">
         <f t="shared" si="13"/>
         <v>0.94736842105263164</v>
       </c>
@@ -30396,17 +30556,31 @@
       <c r="M101" s="4">
         <v>46289</v>
       </c>
-      <c r="N101" s="14">
+      <c r="N101" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q101" s="9"/>
-    </row>
-    <row r="102" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O101" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P101" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q101" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R101" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="S101" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B102" s="4">
         <v>46289</v>
       </c>
-      <c r="C102" s="14">
+      <c r="C102" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>39</v>
       </c>
@@ -30420,37 +30594,51 @@
         <v>12289507</v>
       </c>
       <c r="G102" s="1">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H102" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I102" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>9.8901098901098897E-2</v>
-      </c>
-      <c r="J102" s="14">
+        <v>3.0927835051546393E-2</v>
+      </c>
+      <c r="J102" s="1">
         <f t="shared" si="13"/>
-        <v>0.90109890109890112</v>
+        <v>0.96907216494845361</v>
       </c>
       <c r="K102" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.90109890109890112</v>
+        <v>0.96907216494845361</v>
       </c>
       <c r="M102" s="4">
         <v>46289</v>
       </c>
-      <c r="N102" s="14">
+      <c r="N102" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q102" s="9"/>
-    </row>
-    <row r="103" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O102" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P102" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q102" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R102" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S102" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B103" s="4">
         <v>46289</v>
       </c>
-      <c r="C103" s="14">
+      <c r="C103" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>39</v>
       </c>
@@ -30473,7 +30661,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J103" s="14">
+      <c r="J103" s="1">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
@@ -30484,17 +30672,31 @@
       <c r="M103" s="4">
         <v>46289</v>
       </c>
-      <c r="N103" s="14">
+      <c r="N103" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q103" s="9"/>
-    </row>
-    <row r="104" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O103" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P103" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q103" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R103" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="S103" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B104" s="4">
         <v>46289</v>
       </c>
-      <c r="C104" s="14">
+      <c r="C104" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>39</v>
       </c>
@@ -30517,7 +30719,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>2.1505376344086023E-2</v>
       </c>
-      <c r="J104" s="14">
+      <c r="J104" s="1">
         <f t="shared" si="13"/>
         <v>0.978494623655914</v>
       </c>
@@ -30528,17 +30730,31 @@
       <c r="M104" s="4">
         <v>46289</v>
       </c>
-      <c r="N104" s="14">
+      <c r="N104" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q104" s="9"/>
-    </row>
-    <row r="105" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O104" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P104" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q104" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R104" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="S104" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B105" s="4">
         <v>46289</v>
       </c>
-      <c r="C105" s="14">
+      <c r="C105" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>39</v>
       </c>
@@ -30561,7 +30777,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.43478260869565216</v>
       </c>
-      <c r="J105" s="14">
+      <c r="J105" s="1">
         <f t="shared" si="13"/>
         <v>0.56521739130434789</v>
       </c>
@@ -30572,25 +30788,39 @@
       <c r="M105" s="4">
         <v>46289</v>
       </c>
-      <c r="N105" s="14">
+      <c r="N105" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q105" s="9"/>
-    </row>
-    <row r="106" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O105" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P105" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q105" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R105" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="S105" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B106" s="4">
         <v>46289</v>
       </c>
-      <c r="C106" s="14">
+      <c r="C106" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>39</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E106" s="1">
-        <v>800</v>
+      <c r="E106" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="F106" s="9">
         <v>12289507</v>
@@ -30605,7 +30835,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="J106" s="14">
+      <c r="J106" s="1">
         <f t="shared" si="13"/>
         <v>0.96875</v>
       </c>
@@ -30616,25 +30846,39 @@
       <c r="M106" s="4">
         <v>46289</v>
       </c>
-      <c r="N106" s="14">
+      <c r="N106" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q106" s="9"/>
-    </row>
-    <row r="107" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O106" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P106" s="1">
+        <v>800</v>
+      </c>
+      <c r="Q106" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R106" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S106" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B107" s="4">
         <v>46289</v>
       </c>
-      <c r="C107" s="14">
+      <c r="C107" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>39</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E107" s="1">
-        <v>900</v>
+      <c r="E107" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F107" s="9">
         <v>12289507</v>
@@ -30649,7 +30893,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.25</v>
       </c>
-      <c r="J107" s="14">
+      <c r="J107" s="1">
         <f t="shared" si="13"/>
         <v>0.75</v>
       </c>
@@ -30660,25 +30904,39 @@
       <c r="M107" s="4">
         <v>46289</v>
       </c>
-      <c r="N107" s="14">
+      <c r="N107" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q107" s="9"/>
-    </row>
-    <row r="108" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O107" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P107" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q107" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R107" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="S107" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B108" s="4">
         <v>46289</v>
       </c>
-      <c r="C108" s="14">
+      <c r="C108" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>39</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E108" s="1">
-        <v>1000</v>
+      <c r="E108" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="F108" s="9">
         <v>12289507</v>
@@ -30693,7 +30951,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.29870129870129869</v>
       </c>
-      <c r="J108" s="14">
+      <c r="J108" s="1">
         <f t="shared" si="13"/>
         <v>0.70129870129870131</v>
       </c>
@@ -30704,25 +30962,39 @@
       <c r="M108" s="4">
         <v>46289</v>
       </c>
-      <c r="N108" s="14">
+      <c r="N108" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q108" s="9"/>
-    </row>
-    <row r="109" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O108" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P108" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q108" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R108" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="S108" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B109" s="4">
         <v>46289</v>
       </c>
-      <c r="C109" s="14">
+      <c r="C109" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>39</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E109" s="1">
-        <v>1100</v>
+      <c r="E109" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="F109" s="9">
         <v>12289507</v>
@@ -30737,7 +31009,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>5.7142857142857141E-2</v>
       </c>
-      <c r="J109" s="14">
+      <c r="J109" s="1">
         <f t="shared" si="13"/>
         <v>0.94285714285714284</v>
       </c>
@@ -30748,25 +31020,39 @@
       <c r="M109" s="4">
         <v>46289</v>
       </c>
-      <c r="N109" s="14">
+      <c r="N109" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q109" s="9"/>
-    </row>
-    <row r="110" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O109" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P109" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q109" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R109" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="S109" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B110" s="4">
         <v>46289</v>
       </c>
-      <c r="C110" s="14">
+      <c r="C110" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>39</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E110" s="1">
-        <v>1200</v>
+      <c r="E110" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="F110" s="9">
         <v>12289507</v>
@@ -30781,7 +31067,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.30769230769230771</v>
       </c>
-      <c r="J110" s="14">
+      <c r="J110" s="1">
         <f t="shared" si="13"/>
         <v>0.69230769230769229</v>
       </c>
@@ -30792,259 +31078,1659 @@
       <c r="M110" s="4">
         <v>46289</v>
       </c>
-      <c r="N110" s="14">
+      <c r="N110" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q110" s="9"/>
-    </row>
-    <row r="111" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B111" s="4"/>
-      <c r="C111" s="14"/>
-      <c r="F111" s="9"/>
-      <c r="I111" s="3"/>
-      <c r="J111" s="14"/>
-      <c r="K111" s="5"/>
+      <c r="O110" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P110" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q110" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R110" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="S110" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B111" s="4">
+        <v>46295</v>
+      </c>
+      <c r="C111" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E111" s="1">
+        <v>100</v>
+      </c>
+      <c r="F111" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G111" s="1">
+        <v>37</v>
+      </c>
+      <c r="H111" s="1">
+        <v>4</v>
+      </c>
+      <c r="I111" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.10810810810810811</v>
+      </c>
+      <c r="J111" s="1">
+        <f t="shared" ref="J111:J120" si="14">ABS(G$3-I111)</f>
+        <v>0.89189189189189189</v>
+      </c>
+      <c r="K111" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.89189189189189189</v>
+      </c>
       <c r="M111" s="4">
         <v>46289</v>
       </c>
-      <c r="N111" s="14">
+      <c r="N111" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>39</v>
       </c>
-      <c r="Q111" s="9"/>
-    </row>
-    <row r="112" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B112" s="4"/>
-      <c r="C112" s="14"/>
-      <c r="F112" s="9"/>
-      <c r="I112" s="3"/>
-      <c r="J112" s="14"/>
-      <c r="K112" s="5"/>
-      <c r="M112" s="4"/>
-    </row>
-    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B113" s="4"/>
-      <c r="C113" s="14"/>
-      <c r="F113" s="9"/>
-      <c r="I113" s="3"/>
-      <c r="J113" s="14"/>
-      <c r="K113" s="5"/>
-      <c r="M113" s="4"/>
-    </row>
-    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B114" s="4"/>
-      <c r="C114" s="14"/>
-      <c r="F114" s="9"/>
-      <c r="I114" s="3"/>
-      <c r="J114" s="14"/>
-      <c r="K114" s="5"/>
-      <c r="M114" s="4"/>
-    </row>
-    <row r="115" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B115" s="4"/>
-      <c r="I115" s="3"/>
-      <c r="J115" s="1"/>
-      <c r="K115" s="5"/>
-      <c r="M115" s="4"/>
-    </row>
-    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B116" s="4"/>
-      <c r="I116" s="3"/>
-      <c r="J116" s="1"/>
-      <c r="K116" s="5"/>
-      <c r="M116" s="4"/>
-    </row>
-    <row r="117" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B117" s="4"/>
-      <c r="I117" s="3"/>
-      <c r="J117" s="1"/>
-      <c r="K117" s="5"/>
-      <c r="M117" s="4"/>
-    </row>
-    <row r="118" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B118" s="4"/>
-      <c r="I118" s="3"/>
-      <c r="J118" s="1"/>
-      <c r="K118" s="5"/>
-      <c r="M118" s="4"/>
-    </row>
-    <row r="119" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B119" s="4"/>
-      <c r="I119" s="3"/>
-      <c r="J119" s="1"/>
-      <c r="K119" s="5"/>
-      <c r="M119" s="4"/>
-    </row>
-    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B120" s="4"/>
-      <c r="I120" s="3"/>
-      <c r="J120" s="1"/>
-      <c r="K120" s="5"/>
-      <c r="M120" s="4"/>
-    </row>
-    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B121" s="4"/>
-      <c r="I121" s="3"/>
-      <c r="J121" s="1"/>
-      <c r="K121" s="5"/>
-      <c r="M121" s="4"/>
-    </row>
-    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B122" s="4"/>
-      <c r="I122" s="3"/>
-      <c r="J122" s="1"/>
-      <c r="K122" s="5"/>
-      <c r="M122" s="4"/>
-    </row>
-    <row r="123" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B123" s="4"/>
-      <c r="I123" s="3"/>
-      <c r="J123" s="1"/>
-      <c r="K123" s="5"/>
-      <c r="M123" s="4"/>
-    </row>
-    <row r="124" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B124" s="4"/>
-      <c r="I124" s="3"/>
-      <c r="J124" s="1"/>
-      <c r="K124" s="5"/>
-      <c r="M124" s="4"/>
-    </row>
-    <row r="125" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B125" s="4"/>
-      <c r="I125" s="3"/>
-      <c r="J125" s="1"/>
-      <c r="K125" s="5"/>
-      <c r="M125" s="4"/>
-    </row>
-    <row r="126" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B126" s="4"/>
-      <c r="I126" s="3"/>
-      <c r="J126" s="1"/>
-      <c r="K126" s="5"/>
-      <c r="M126" s="4"/>
-    </row>
-    <row r="127" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B127" s="4"/>
-      <c r="I127" s="3"/>
-      <c r="J127" s="1"/>
-      <c r="K127" s="5"/>
-      <c r="M127" s="4"/>
-    </row>
-    <row r="128" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B128" s="4"/>
-      <c r="I128" s="3"/>
-      <c r="J128" s="1"/>
-      <c r="K128" s="5"/>
-      <c r="M128" s="4"/>
-    </row>
-    <row r="129" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B129" s="4"/>
-      <c r="I129" s="3"/>
-      <c r="J129" s="1"/>
-      <c r="K129" s="5"/>
-      <c r="M129" s="4"/>
-    </row>
-    <row r="130" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B130" s="4"/>
-      <c r="I130" s="3"/>
-      <c r="J130" s="1"/>
-      <c r="K130" s="5"/>
-      <c r="M130" s="4"/>
-    </row>
-    <row r="131" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B131" s="4"/>
-      <c r="I131" s="3"/>
-      <c r="J131" s="1"/>
-      <c r="K131" s="5"/>
-      <c r="M131" s="4"/>
-    </row>
-    <row r="132" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B132" s="4"/>
-      <c r="I132" s="3"/>
-      <c r="J132" s="1"/>
-      <c r="K132" s="5"/>
-      <c r="M132" s="4"/>
-    </row>
-    <row r="133" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B133" s="4"/>
-      <c r="I133" s="3"/>
-      <c r="J133" s="1"/>
-      <c r="K133" s="5"/>
-      <c r="M133" s="4"/>
-    </row>
-    <row r="134" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B134" s="4"/>
-      <c r="I134" s="3"/>
-      <c r="J134" s="1"/>
-      <c r="K134" s="5"/>
-      <c r="M134" s="4"/>
-    </row>
-    <row r="135" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B135" s="4"/>
-      <c r="I135" s="3"/>
-      <c r="J135" s="1"/>
-      <c r="K135" s="5"/>
-      <c r="M135" s="4"/>
-    </row>
-    <row r="136" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="O111" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P111" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q111" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R111" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="S111" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B112" s="4">
+        <v>46295</v>
+      </c>
+      <c r="C112" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E112" s="1">
+        <v>150</v>
+      </c>
+      <c r="F112" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G112" s="1">
+        <v>37</v>
+      </c>
+      <c r="H112" s="1">
+        <v>0</v>
+      </c>
+      <c r="I112" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J112" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="K112" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M112" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N112" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="O112" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P112" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q112" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R112" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="S112" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B113" s="4">
+        <v>46295</v>
+      </c>
+      <c r="C113" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E113" s="1">
+        <v>200</v>
+      </c>
+      <c r="F113" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G113" s="1">
+        <v>35</v>
+      </c>
+      <c r="H113" s="1">
+        <v>0</v>
+      </c>
+      <c r="I113" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J113" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="K113" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M113" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N113" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="O113" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P113" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q113" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R113" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="S113" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="114" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B114" s="4">
+        <v>46295</v>
+      </c>
+      <c r="C114" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E114" s="1">
+        <v>300</v>
+      </c>
+      <c r="F114" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G114" s="1">
+        <v>35</v>
+      </c>
+      <c r="H114" s="1">
+        <v>0</v>
+      </c>
+      <c r="I114" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J114" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="K114" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M114" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N114" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="O114" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P114" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q114" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R114" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="S114" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B115" s="4">
+        <v>46295</v>
+      </c>
+      <c r="C115" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F115" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G115" s="1">
+        <v>18</v>
+      </c>
+      <c r="H115" s="1">
+        <v>6</v>
+      </c>
+      <c r="I115" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J115" s="1">
+        <f t="shared" si="14"/>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="K115" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="M115" s="4">
+        <v>46289</v>
+      </c>
+      <c r="N115" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>39</v>
+      </c>
+      <c r="O115" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P115" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q115" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R115" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="S115" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B116" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C116" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E116" s="1">
+        <v>100</v>
+      </c>
+      <c r="F116" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G116" s="1">
+        <v>113</v>
+      </c>
+      <c r="H116" s="1">
+        <v>0</v>
+      </c>
+      <c r="I116" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J116" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="K116" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M116" s="4">
+        <v>46295</v>
+      </c>
+      <c r="N116" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P116" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q116" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R116" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S116" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B117" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C117" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E117" s="1">
+        <v>150</v>
+      </c>
+      <c r="F117" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G117" s="1">
+        <v>113</v>
+      </c>
+      <c r="H117" s="1">
+        <v>10</v>
+      </c>
+      <c r="I117" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>8.8495575221238937E-2</v>
+      </c>
+      <c r="J117" s="1">
+        <f t="shared" si="14"/>
+        <v>0.91150442477876104</v>
+      </c>
+      <c r="K117" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.91150442477876104</v>
+      </c>
+      <c r="M117" s="4">
+        <v>46295</v>
+      </c>
+      <c r="N117" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O117" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P117" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q117" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R117" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="S117" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B118" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C118" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E118" s="1">
+        <v>200</v>
+      </c>
+      <c r="F118" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G118" s="1">
+        <v>113</v>
+      </c>
+      <c r="H118" s="1">
+        <v>11</v>
+      </c>
+      <c r="I118" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>9.7345132743362831E-2</v>
+      </c>
+      <c r="J118" s="1">
+        <f t="shared" si="14"/>
+        <v>0.90265486725663713</v>
+      </c>
+      <c r="K118" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.90265486725663713</v>
+      </c>
+      <c r="M118" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N118" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O118" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P118" s="1">
+        <v>150</v>
+      </c>
+      <c r="Q118" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R118" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="S118" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B119" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C119" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E119" s="1">
+        <v>300</v>
+      </c>
+      <c r="F119" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G119" s="1">
+        <v>113</v>
+      </c>
+      <c r="H119" s="1">
+        <v>0</v>
+      </c>
+      <c r="I119" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J119" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="K119" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M119" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N119" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O119" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P119" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q119" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R119" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="S119" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B120" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C120" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F120" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G120" s="1">
+        <v>72</v>
+      </c>
+      <c r="H120" s="1">
+        <v>30</v>
+      </c>
+      <c r="I120" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J120" s="1">
+        <f t="shared" si="14"/>
+        <v>0.58333333333333326</v>
+      </c>
+      <c r="K120" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.58333333333333326</v>
+      </c>
+      <c r="M120" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N120" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O120" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P120" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q120" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R120" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="S120" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B121" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C121" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E121" s="1">
+        <v>100</v>
+      </c>
+      <c r="F121" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G121" s="1">
+        <v>71</v>
+      </c>
+      <c r="H121" s="1">
+        <v>0</v>
+      </c>
+      <c r="I121" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J121" s="14">
+        <f t="shared" ref="J121:J127" si="15">ABS(G$3-I121)</f>
+        <v>1</v>
+      </c>
+      <c r="K121" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M121" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N121" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O121" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P121" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q121" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R121" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S121" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B122" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C122" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E122" s="1">
+        <v>200</v>
+      </c>
+      <c r="F122" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G122" s="1">
+        <v>68</v>
+      </c>
+      <c r="H122" s="1">
+        <v>3</v>
+      </c>
+      <c r="I122" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>4.4117647058823532E-2</v>
+      </c>
+      <c r="J122" s="14">
+        <f t="shared" si="15"/>
+        <v>0.95588235294117652</v>
+      </c>
+      <c r="K122" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.95588235294117652</v>
+      </c>
+      <c r="M122" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N122" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O122" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P122" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q122" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R122" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="S122" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B123" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C123" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E123" s="1">
+        <v>300</v>
+      </c>
+      <c r="F123" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G123" s="1">
+        <v>68</v>
+      </c>
+      <c r="H123" s="1">
+        <v>3</v>
+      </c>
+      <c r="I123" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>4.4117647058823532E-2</v>
+      </c>
+      <c r="J123" s="14">
+        <f t="shared" si="15"/>
+        <v>0.95588235294117652</v>
+      </c>
+      <c r="K123" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.95588235294117652</v>
+      </c>
+      <c r="M123" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N123" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O123" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P123" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q123" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R123" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="S123" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B124" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C124" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E124" s="1">
+        <v>400</v>
+      </c>
+      <c r="F124" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G124" s="1">
+        <v>68</v>
+      </c>
+      <c r="H124" s="1">
+        <v>0</v>
+      </c>
+      <c r="I124" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J124" s="14">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="K124" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M124" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N124" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O124" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P124" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q124" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R124" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="S124" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B125" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C125" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E125" s="1">
+        <v>500</v>
+      </c>
+      <c r="F125" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G125" s="1">
+        <v>68</v>
+      </c>
+      <c r="H125" s="1">
+        <v>0</v>
+      </c>
+      <c r="I125" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J125" s="14">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="K125" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M125" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N125" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O125" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P125" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q125" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R125" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="S125" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B126" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C126" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E126" s="1">
+        <v>600</v>
+      </c>
+      <c r="F126" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G126" s="1">
+        <v>68</v>
+      </c>
+      <c r="H126" s="1">
+        <v>0</v>
+      </c>
+      <c r="I126" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J126" s="14">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="K126" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M126" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N126" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O126" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P126" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q126" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R126" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="S126" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B127" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C127" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E127" s="1">
+        <v>700</v>
+      </c>
+      <c r="F127" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G127" s="1">
+        <v>55</v>
+      </c>
+      <c r="H127" s="1">
+        <v>3</v>
+      </c>
+      <c r="I127" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>5.4545454545454543E-2</v>
+      </c>
+      <c r="J127" s="14">
+        <f t="shared" si="15"/>
+        <v>0.94545454545454544</v>
+      </c>
+      <c r="K127" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.94545454545454544</v>
+      </c>
+      <c r="M127" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N127" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O127" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P127" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q127" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R127" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="S127" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B128" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C128" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E128" s="1">
+        <v>800</v>
+      </c>
+      <c r="F128" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G128" s="1">
+        <v>54</v>
+      </c>
+      <c r="H128" s="1">
+        <v>0</v>
+      </c>
+      <c r="I128" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J128" s="14">
+        <f t="shared" ref="J128:J133" si="16">ABS(G$3-I128)</f>
+        <v>1</v>
+      </c>
+      <c r="K128" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M128" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N128" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O128" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P128" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q128" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R128" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="S128" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B129" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C129" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F129" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G129" s="1">
+        <v>54</v>
+      </c>
+      <c r="H129" s="1">
+        <v>27</v>
+      </c>
+      <c r="I129" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.5</v>
+      </c>
+      <c r="J129" s="14">
+        <f t="shared" si="16"/>
+        <v>0.5</v>
+      </c>
+      <c r="K129" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.5</v>
+      </c>
+      <c r="M129" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N129" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O129" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P129" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q129" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R129" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="S129" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B130" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C130" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F130" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G130" s="1">
+        <v>53</v>
+      </c>
+      <c r="H130" s="1">
+        <v>15</v>
+      </c>
+      <c r="I130" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.28301886792452829</v>
+      </c>
+      <c r="J130" s="14">
+        <f t="shared" si="16"/>
+        <v>0.71698113207547176</v>
+      </c>
+      <c r="K130" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.71698113207547176</v>
+      </c>
+      <c r="M130" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N130" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O130" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P130" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q130" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R130" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="S130" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B131" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C131" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F131" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G131" s="1">
+        <v>81</v>
+      </c>
+      <c r="H131" s="1">
+        <v>3</v>
+      </c>
+      <c r="I131" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>3.7037037037037035E-2</v>
+      </c>
+      <c r="J131" s="14">
+        <f t="shared" si="16"/>
+        <v>0.96296296296296302</v>
+      </c>
+      <c r="K131" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.96296296296296302</v>
+      </c>
+      <c r="M131" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N131" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O131" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P131" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q131" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R131" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="S131" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B132" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C132" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F132" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G132" s="1">
+        <v>13</v>
+      </c>
+      <c r="H132" s="1">
+        <v>0</v>
+      </c>
+      <c r="I132" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J132" s="14">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="K132" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M132" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N132" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O132" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P132" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q132" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R132" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="S132" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B133" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C133" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F133" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G133" s="1">
+        <v>19</v>
+      </c>
+      <c r="H133" s="1">
+        <v>2</v>
+      </c>
+      <c r="I133" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="J133" s="14">
+        <f t="shared" si="16"/>
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="K133" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="M133" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N133" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O133" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P133" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q133" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R133" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="S133" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B134" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C134" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F134" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G134" s="1">
+        <v>21</v>
+      </c>
+      <c r="H134" s="1">
+        <v>12</v>
+      </c>
+      <c r="I134" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="J134" s="14">
+        <f t="shared" ref="J134:J135" si="17">ABS(G$3-I134)</f>
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="K134" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="M134" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N134" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O134" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P134" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q134" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R134" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="S134" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B135" s="4">
+        <v>46297</v>
+      </c>
+      <c r="C135" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>40</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F135" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G135" s="1">
+        <v>48</v>
+      </c>
+      <c r="H135" s="1">
+        <v>0</v>
+      </c>
+      <c r="I135" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J135" s="14">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="K135" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M135" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N135" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O135" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P135" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q135" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R135" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="S135" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B136" s="4"/>
       <c r="I136" s="3"/>
       <c r="J136" s="1"/>
       <c r="K136" s="5"/>
-      <c r="M136" s="4"/>
-    </row>
-    <row r="137" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M136" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N136" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O136" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P136" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q136" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R136" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="S136" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B137" s="4"/>
       <c r="I137" s="3"/>
       <c r="J137" s="1"/>
       <c r="K137" s="5"/>
-      <c r="M137" s="4"/>
-    </row>
-    <row r="138" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M137" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N137" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O137" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P137" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q137" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R137" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="S137" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B138" s="4"/>
       <c r="I138" s="3"/>
       <c r="J138" s="1"/>
       <c r="K138" s="5"/>
-      <c r="M138" s="4"/>
-    </row>
-    <row r="139" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M138" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N138" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O138" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P138" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q138" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R138" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="S138" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B139" s="4"/>
       <c r="I139" s="3"/>
       <c r="J139" s="1"/>
       <c r="K139" s="5"/>
-      <c r="M139" s="4"/>
-    </row>
-    <row r="140" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M139" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N139" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O139" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P139" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q139" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R139" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="S139" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B140" s="4"/>
       <c r="I140" s="3"/>
       <c r="J140" s="1"/>
       <c r="K140" s="5"/>
-      <c r="M140" s="4"/>
-    </row>
-    <row r="141" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M140" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N140" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O140" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P140" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q140" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R140" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="S140" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B141" s="4"/>
       <c r="I141" s="3"/>
       <c r="J141" s="1"/>
       <c r="K141" s="5"/>
-      <c r="M141" s="4"/>
-    </row>
-    <row r="142" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M141" s="4">
+        <v>46297</v>
+      </c>
+      <c r="N141" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>40</v>
+      </c>
+      <c r="O141" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P141" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q141" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R141" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="S141" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="142" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B142" s="4"/>
       <c r="I142" s="3"/>
       <c r="J142" s="1"/>
       <c r="K142" s="5"/>
       <c r="M142" s="4"/>
     </row>
-    <row r="143" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B143" s="4"/>
       <c r="I143" s="3"/>
       <c r="J143" s="1"/>
       <c r="K143" s="5"/>
       <c r="M143" s="4"/>
     </row>
-    <row r="144" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B144" s="4"/>
       <c r="I144" s="3"/>
       <c r="J144" s="1"/>

--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\5_MB MMA\09_Information\10_FTQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74F80C2-175A-49A3-8903-3A7F3DD90E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D6CB46-623B-4264-B4F4-8E4D5E80782D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE DE DATOS" sheetId="1" r:id="rId1"/>
@@ -490,7 +490,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -530,9 +530,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -31682,7 +31679,7 @@
       <c r="B121" s="4">
         <v>46297</v>
       </c>
-      <c r="C121" s="14">
+      <c r="C121" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>40</v>
       </c>
@@ -31705,7 +31702,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J121" s="14">
+      <c r="J121" s="1">
         <f t="shared" ref="J121:J127" si="15">ABS(G$3-I121)</f>
         <v>1</v>
       </c>
@@ -31740,7 +31737,7 @@
       <c r="B122" s="4">
         <v>46297</v>
       </c>
-      <c r="C122" s="14">
+      <c r="C122" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>40</v>
       </c>
@@ -31763,7 +31760,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>4.4117647058823532E-2</v>
       </c>
-      <c r="J122" s="14">
+      <c r="J122" s="1">
         <f t="shared" si="15"/>
         <v>0.95588235294117652</v>
       </c>
@@ -31798,7 +31795,7 @@
       <c r="B123" s="4">
         <v>46297</v>
       </c>
-      <c r="C123" s="14">
+      <c r="C123" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>40</v>
       </c>
@@ -31821,7 +31818,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>4.4117647058823532E-2</v>
       </c>
-      <c r="J123" s="14">
+      <c r="J123" s="1">
         <f t="shared" si="15"/>
         <v>0.95588235294117652</v>
       </c>
@@ -31856,7 +31853,7 @@
       <c r="B124" s="4">
         <v>46297</v>
       </c>
-      <c r="C124" s="14">
+      <c r="C124" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>40</v>
       </c>
@@ -31879,7 +31876,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J124" s="14">
+      <c r="J124" s="1">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
@@ -31890,7 +31887,7 @@
       <c r="M124" s="4">
         <v>46297</v>
       </c>
-      <c r="N124" s="14">
+      <c r="N124" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -31914,7 +31911,7 @@
       <c r="B125" s="4">
         <v>46297</v>
       </c>
-      <c r="C125" s="14">
+      <c r="C125" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>40</v>
       </c>
@@ -31937,7 +31934,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J125" s="14">
+      <c r="J125" s="1">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
@@ -31948,7 +31945,7 @@
       <c r="M125" s="4">
         <v>46297</v>
       </c>
-      <c r="N125" s="14">
+      <c r="N125" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -31972,7 +31969,7 @@
       <c r="B126" s="4">
         <v>46297</v>
       </c>
-      <c r="C126" s="14">
+      <c r="C126" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>40</v>
       </c>
@@ -31995,7 +31992,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J126" s="14">
+      <c r="J126" s="1">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
@@ -32006,7 +32003,7 @@
       <c r="M126" s="4">
         <v>46297</v>
       </c>
-      <c r="N126" s="14">
+      <c r="N126" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32030,7 +32027,7 @@
       <c r="B127" s="4">
         <v>46297</v>
       </c>
-      <c r="C127" s="14">
+      <c r="C127" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>40</v>
       </c>
@@ -32053,7 +32050,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>5.4545454545454543E-2</v>
       </c>
-      <c r="J127" s="14">
+      <c r="J127" s="1">
         <f t="shared" si="15"/>
         <v>0.94545454545454544</v>
       </c>
@@ -32064,7 +32061,7 @@
       <c r="M127" s="4">
         <v>46297</v>
       </c>
-      <c r="N127" s="14">
+      <c r="N127" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32088,7 +32085,7 @@
       <c r="B128" s="4">
         <v>46297</v>
       </c>
-      <c r="C128" s="14">
+      <c r="C128" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>40</v>
       </c>
@@ -32111,7 +32108,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J128" s="14">
+      <c r="J128" s="1">
         <f t="shared" ref="J128:J133" si="16">ABS(G$3-I128)</f>
         <v>1</v>
       </c>
@@ -32122,7 +32119,7 @@
       <c r="M128" s="4">
         <v>46297</v>
       </c>
-      <c r="N128" s="14">
+      <c r="N128" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32146,7 +32143,7 @@
       <c r="B129" s="4">
         <v>46297</v>
       </c>
-      <c r="C129" s="14">
+      <c r="C129" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>40</v>
       </c>
@@ -32169,7 +32166,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.5</v>
       </c>
-      <c r="J129" s="14">
+      <c r="J129" s="1">
         <f t="shared" si="16"/>
         <v>0.5</v>
       </c>
@@ -32180,7 +32177,7 @@
       <c r="M129" s="4">
         <v>46297</v>
       </c>
-      <c r="N129" s="14">
+      <c r="N129" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32204,7 +32201,7 @@
       <c r="B130" s="4">
         <v>46297</v>
       </c>
-      <c r="C130" s="14">
+      <c r="C130" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>40</v>
       </c>
@@ -32227,7 +32224,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.28301886792452829</v>
       </c>
-      <c r="J130" s="14">
+      <c r="J130" s="1">
         <f t="shared" si="16"/>
         <v>0.71698113207547176</v>
       </c>
@@ -32238,7 +32235,7 @@
       <c r="M130" s="4">
         <v>46297</v>
       </c>
-      <c r="N130" s="14">
+      <c r="N130" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32262,7 +32259,7 @@
       <c r="B131" s="4">
         <v>46297</v>
       </c>
-      <c r="C131" s="14">
+      <c r="C131" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>40</v>
       </c>
@@ -32285,7 +32282,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>3.7037037037037035E-2</v>
       </c>
-      <c r="J131" s="14">
+      <c r="J131" s="1">
         <f t="shared" si="16"/>
         <v>0.96296296296296302</v>
       </c>
@@ -32296,7 +32293,7 @@
       <c r="M131" s="4">
         <v>46297</v>
       </c>
-      <c r="N131" s="14">
+      <c r="N131" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32320,7 +32317,7 @@
       <c r="B132" s="4">
         <v>46297</v>
       </c>
-      <c r="C132" s="14">
+      <c r="C132" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>40</v>
       </c>
@@ -32334,7 +32331,7 @@
         <v>12289507</v>
       </c>
       <c r="G132" s="1">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="H132" s="1">
         <v>0</v>
@@ -32343,7 +32340,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J132" s="14">
+      <c r="J132" s="1">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
@@ -32354,7 +32351,7 @@
       <c r="M132" s="4">
         <v>46297</v>
       </c>
-      <c r="N132" s="14">
+      <c r="N132" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32378,7 +32375,7 @@
       <c r="B133" s="4">
         <v>46297</v>
       </c>
-      <c r="C133" s="14">
+      <c r="C133" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>40</v>
       </c>
@@ -32392,27 +32389,27 @@
         <v>12289507</v>
       </c>
       <c r="G133" s="1">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H133" s="1">
         <v>2</v>
       </c>
       <c r="I133" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.10526315789473684</v>
-      </c>
-      <c r="J133" s="14">
+        <v>6.4516129032258063E-2</v>
+      </c>
+      <c r="J133" s="1">
         <f t="shared" si="16"/>
-        <v>0.89473684210526316</v>
+        <v>0.93548387096774199</v>
       </c>
       <c r="K133" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.89473684210526316</v>
+        <v>0.93548387096774199</v>
       </c>
       <c r="M133" s="4">
         <v>46297</v>
       </c>
-      <c r="N133" s="14">
+      <c r="N133" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32436,7 +32433,7 @@
       <c r="B134" s="4">
         <v>46297</v>
       </c>
-      <c r="C134" s="14">
+      <c r="C134" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>40</v>
       </c>
@@ -32450,27 +32447,27 @@
         <v>12289507</v>
       </c>
       <c r="G134" s="1">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="H134" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I134" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="J134" s="14">
+        <v>0.34042553191489361</v>
+      </c>
+      <c r="J134" s="1">
         <f t="shared" ref="J134:J135" si="17">ABS(G$3-I134)</f>
-        <v>0.4285714285714286</v>
+        <v>0.65957446808510634</v>
       </c>
       <c r="K134" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.4285714285714286</v>
+        <v>0.65957446808510634</v>
       </c>
       <c r="M134" s="4">
         <v>46297</v>
       </c>
-      <c r="N134" s="14">
+      <c r="N134" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32494,7 +32491,7 @@
       <c r="B135" s="4">
         <v>46297</v>
       </c>
-      <c r="C135" s="14">
+      <c r="C135" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>40</v>
       </c>
@@ -32517,7 +32514,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J135" s="14">
+      <c r="J135" s="1">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
@@ -32528,7 +32525,7 @@
       <c r="M135" s="4">
         <v>46297</v>
       </c>
-      <c r="N135" s="14">
+      <c r="N135" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32556,7 +32553,7 @@
       <c r="M136" s="4">
         <v>46297</v>
       </c>
-      <c r="N136" s="14">
+      <c r="N136" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32584,7 +32581,7 @@
       <c r="M137" s="4">
         <v>46297</v>
       </c>
-      <c r="N137" s="14">
+      <c r="N137" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32612,7 +32609,7 @@
       <c r="M138" s="4">
         <v>46297</v>
       </c>
-      <c r="N138" s="14">
+      <c r="N138" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32640,7 +32637,7 @@
       <c r="M139" s="4">
         <v>46297</v>
       </c>
-      <c r="N139" s="14">
+      <c r="N139" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32668,7 +32665,7 @@
       <c r="M140" s="4">
         <v>46297</v>
       </c>
-      <c r="N140" s="14">
+      <c r="N140" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32696,7 +32693,7 @@
       <c r="M141" s="4">
         <v>46297</v>
       </c>
-      <c r="N141" s="14">
+      <c r="N141" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>40</v>
       </c>
@@ -32713,7 +32710,7 @@
         <v>114</v>
       </c>
       <c r="S141" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="142" spans="2:19" x14ac:dyDescent="0.3">
